--- a/BCA_tracker_only_BCA.xlsx
+++ b/BCA_tracker_only_BCA.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1802,113 +1802,6 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>US-CA-ELEC</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>California (United States - sub-national)</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Cap-and-Invest (formerly Cap-and-Trade): compliance obligation on imported electricity</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>BCA</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>In force / operational</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>In Force</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>2013-01-01 (compliance obligation); regulation adopted by CARB in 2011, electricity sector included from 2012.</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>Prevent emissions leakage in the electricity sector by placing the same carbon compliance obligation on electricity imported into California as on in-state generation under the AB 32 (Global Warming Solutions Act) programme.</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>YES - generation emissions attributed to imported electricity. Specified-source imports use resource-specific emission rates; unspecified imports use a default emission factor.</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>N/A - the covered good is electricity itself.</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>NO.</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>Covers IMPORTED ELECTRICITY ONLY, not goods. Uses a 'first deliverer' design treating importers and in-state generators alike. Effectiveness is constrained by 'resource shuffling' - contractual reattribution of clean power to California - which the regulation prohibits but has struggled to police; roughly half the programme's reported reductions have been attributed to imported electricity.</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="inlineStr">
-        <is>
-          <t>N/A - applies to imports from other US states and Canadian provinces in the Western Interconnection. No origin carbon-price credit mechanism of the EU/UK type.</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="inlineStr">
-        <is>
-          <t>YES - a default emission factor applies to unspecified-source imports; specified sources may report resource-specific rates.</t>
-        </is>
-      </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>Programme-wide reporting thresholds under the Mandatory Reporting Regulation apply; there is no value-based import de minimis of the EU/UK type.</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="inlineStr">
-        <is>
-          <t>Electricity importers (first deliverers) surrender California allowances for the emissions attributed to the power they import, at the same allowance price as in-state generators.</t>
-        </is>
-      </c>
-      <c r="Q14" s="5" t="inlineStr">
-        <is>
-          <t>Auction proceeds flow to the California Greenhouse Gas Reduction Fund. There is no separate BCA revenue stream.</t>
-        </is>
-      </c>
-      <c r="R14" s="5" t="inlineStr">
-        <is>
-          <t>California Air Resources Board - Cap-and-Invest Program (formerly Cap-and-Trade), under AB 32</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="inlineStr">
-        <is>
-          <t>https://ww2.arb.ca.gov/our-work/programs/cap-and-invest-program</t>
-        </is>
-      </c>
-      <c r="T14" s="5" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U14" s="5" t="inlineStr">
-        <is>
-          <t>ADDED 2026-09. The oldest operating border carbon adjustment anywhere - sub-national and electricity-only. Widely cited in the literature as the first BCA in practice; delete this row if the tracker is national-level only.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:U1"/>
@@ -2440,7 +2333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3204,28 +3097,6 @@
       <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Trial declaration only - no charge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>US-CA-ELEC</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>2716</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>Imported electricity only. HS code shown for cross-instrument comparability; the Californian obligation is defined by MWh delivered, not by tariff classification.</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4503,60 +4374,6 @@
       <c r="E47" s="4" t="inlineStr">
         <is>
           <t>https://climateinstitute.ca/news/mou-with-alberta-puts-canadas-commitment-to-net-zero-emissions-by-2050-firmly-out-of-reach/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>US-CA-ELEC</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>CARB adopts the cap-and-trade regulation, covering imported electricity via a 'first deliverer' obligation</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>Importers and in-state generators treated alike.</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>https://ww2.arb.ca.gov/our-work/programs/cap-and-invest-program</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>US-CA-ELEC</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>2013-01</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Compliance obligation takes effect, including on imported electricity</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>The first operating border carbon adjustment anywhere.</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>https://ww2.arb.ca.gov/our-work/programs/cap-and-invest-program</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5159,33 +4976,6 @@
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>US-CA-ELEC</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>CARB - Cap-and-Invest Program (formerly Cap-and-Trade)</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Regulatory page</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>https://ww2.arb.ca.gov/our-work/programs/cap-and-invest-program</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>2026</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5052,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>EU CBAM, Serbia, California (electricity)</t>
+          <t>EU CBAM, Serbia</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5271,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>EU, UK, Serbia, Norway, Australia (recommended), Thailand (draft), US bills, California</t>
+          <t>EU, UK, Serbia, Norway, Australia (recommended), Thailand (draft), US bills</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5472,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>EU, Serbia (domestic tax only), Norway, California. EXCLUDED from the UK CBAM and from the Serbian import tax.</t>
+          <t>EU, Serbia (domestic tax only), Norway. EXCLUDED from the UK CBAM and from the Serbian import tax.</t>
         </is>
       </c>
     </row>

--- a/BCA_tracker_only_BCA.xlsx
+++ b/BCA_tracker_only_BCA.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>50 tonnes of imported CBAM goods per importer per year (mass-based; introduced by Reg (EU) 2025/2083, replacing the earlier value-based exemption). Expected to exempt c.182,000 additional importers while still covering 99% of in-scope emissions.</t>
+          <t>50 tonnes of imported CBAM goods per importer per year (cumulative net mass). IMPORTANT: the threshold does NOT apply to hydrogen or electricity, which remain in scope at any volume. Introduced by Reg (EU) 2025/2083, replacing the earlier EUR 150-per-consignment exemption. Expected to exempt c.182,000 additional importers while still covering 99% of in-scope emissions.</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Unavailable - no commencement date. The recommendation feeds into the 2026-27 review of the Safeguard Mechanism.</t>
+          <t>Unavailable - no commencement date. Final report released 13 February 2026; recommendations feed into the 2026-27 review of the Safeguard Mechanism.</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Export BCAs expressly RULED OUT as incompatible with Australia's national emissions-reduction targets and its international trade law obligations. The review also concluded that neither public investment nor mandatory emissions product standards would be sufficient as stand-alone responses to leakage.</t>
+          <t>Export BCAs / rebates expressly RULED OUT as incompatible with Australia's emissions-reduction targets and international trade law obligations. The review also recommends REMOVING Trade Exposed Baseline Adjustment (TEBA) provisions for any commodity brought within the BCA, so that facilities are not shielded twice. It concluded that neither public investment nor mandatory emissions product standards would suffice as stand-alone responses to leakage.</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>Department of Climate Change, Energy, the Environment and Water - Carbon Leakage Review, final report (February 2026)</t>
+          <t>Department of Climate Change, Energy, the Environment and Water - Carbon Leakage Review, final report (released 13 February 2026; review conducted July 2023 - March 2025)</t>
         </is>
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>https://www.dcceew.gov.au/climate-change/emissions-reduction/safeguard-mechanism</t>
+          <t>https://www.dcceew.gov.au/climate-change/publications/carbon-leakage-review</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>A recommendation of an independent review, NOT government policy. Initial coverage cement and clinker; lime, ammonia and derivatives, iron &amp; steel and glass flagged as possible future additions.</t>
+          <t>A recommendation of an independent review, NOT government policy. Initial coverage cement and clinker; lime, hydrogen, ammonia and derivatives, iron &amp; steel and glass flagged as possible future additions. Clinker was identified as the most exposed commodity.</t>
         </is>
       </c>
     </row>
@@ -994,47 +994,47 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Not specified in published material - confirm against the Official Gazette text and implementing rules.</t>
+          <t>Not specified in published material - the laws work from embedded production emissions net of a reference emission value rather than from the GHG Protocol scopes. Confirm against the Official Gazette text.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Not specified in published material - confirm against the Official Gazette text and implementing rules.</t>
+          <t>Not specified in published material - no precursor rule of the EU/UK type has been identified. Confirm against the Official Gazette text.</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Covered sectors mirror the EU CBAM (cement, fertilizers, iron &amp; steel, aluminium, hydrogen) but ELECTRICITY IS EXCLUDED from the import tax because of technical limitations and the absence of a precise taxing methodology - a notable divergence from the EU model Serbia otherwise follows.</t>
+          <t>Covers FOUR product groups: iron &amp; steel, cement, fertilizers and aluminium. HYDROGEN IS NOT COVERED by the import tax and ELECTRICITY IS EXCLUDED (technical limitations and the absence of a precise taxing methodology) - two divergences from the EU model Serbia otherwise follows closely. The companion domestic GHG Emissions Tax does cover electricity producers.</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>YES - tax credit available where a carbon levy has already been paid in the country of origin.</t>
+          <t>YES - liability reduced where an emissions charge has already been paid in the country of origin, on submission of appropriate evidence.</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Not yet specified in published material.</t>
+          <t>YES - default values are provided in the legislation. Importers may instead report independently verified actual emissions; verification must be carried out by bodies accredited under the International Accreditation Forum (IAF) system.</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>Not specified in published material.</t>
+          <t>Importers of fewer than 5 tonnes of a covered product in a calendar year are not taxpayers. Note this is far tighter than the EU threshold (50 tonnes).</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>Tax assessed on emissions embedded in the production of imported goods, less a credit for any carbon levy paid in the country of origin. Detailed implementing methodology not yet published.</t>
+          <t>Tax base = actual or default embedded emissions of the imported product, reduced by prescribed reference emission values, taxed at EUR 4 per tonne CO2e (converted to dinars at the National Bank of Serbia middle rate on the last day of the tax period). Liability is reduced by any emissions charge already paid at origin. Annual return due 31 May for the preceding year. The EUR 4 rate is roughly 5% of the Q1 2026 EU CBAM certificate price of EUR 75.36.</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>Not specified.</t>
+          <t>Not specified in the law. The companion GHG Emissions Tax offers electricity producers a 20% tax credit for eligible decarbonisation investment, capped at 80% of liability.</t>
         </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>Official Gazette of the Republic of Serbia - Law on the Tax on Imports of Carbon-Intensive Products (2025)</t>
+          <t>Official Gazette of the Republic of Serbia - Law on the Tax on Imports of Carbon-Intensive Products (adopted by the National Assembly, December 2025)</t>
         </is>
       </c>
       <c r="S6" s="4" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>The second BCA in the world to enter into force. Adopted as one of a pair with the domestic Law on Greenhouse Gas Emissions Tax; Serbia is among the most EU CBAM-exposed economies (7.1% of its global exports).</t>
+          <t>The second BCA in the world to enter into force, at EUR 4/tCO2e. Adopted as one of a pair with the domestic Law on Greenhouse Gas Emissions Tax; Serbia is among the most EU CBAM-exposed economies (7.1% of its global exports). Several implementing bylaws were still outstanding at adoption.</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Foreign Pollution Fee Act of 2025 (Cassidy / Graham)</t>
+          <t>Foreign Pollution Fee Act of 2025 (S. 1325, Cassidy / Graham)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1193,67 +1193,67 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Unavailable - not enacted as at September 2026.</t>
+          <t>Unavailable - not enacted. Introduced in the Senate 8 April 2025 as S. 1325 (119th Congress); referred to the Committee on Finance.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Impose fees on certain imported carbon-intensive products based on the emissions intensity of their production abroad relative to US benchmarks.</t>
+          <t>Impose a fee on certain imported products based on the pollution intensity associated with their production, relative to the pollution intensity of producing the same product in the United States. (S. 1325, long title)</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Emissions intensity of production measured against US sectoral benchmarks. Detailed emissions-scope definitions sit in the discussion draft and have not been settled in enacted text.</t>
+          <t>Pollution intensity of production, benchmarked against the US baseline pollution intensity for the same covered product. GHGs measured as CO2 equivalent over a 100-year GWP per 40 CFR Part 98 subpart A table A-1.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Not specified in the discussion draft.</t>
+          <t>Not separately specified in the bill as introduced.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Not specified in the discussion draft.</t>
+          <t>Not separately specified in the bill as introduced.</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>NOT linked to an economy-wide domestic carbon price - there is no US carbon price to which the border charge corresponds. Commentators read the bill as partly geopolitical (China-focused) rather than purely a leakage measure. Product list in the discussion draft is broader than the EU/UK lists; verify against final bill text before relying on it.</t>
+          <t>NOT linked to an economy-wide domestic carbon price and NOT levied on US producers - the fee falls on imports only, benchmarked to US intensity. Covers EIGHT product categories. A 2x fee multiplier applies to covered products from non-market economies (aimed at China). Anti-evasion powers allow the Secretary of Commerce to prohibit imports from an evading country or producer. Framed by its sponsors primarily in trade and national-security terms rather than climate terms.</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>N/A - because the fee is benchmarked to US emissions intensity rather than to a domestic carbon price, the draft contains no equivalent carbon-price deduction of the EU/UK type.</t>
+          <t>NO carbon-price deduction of the EU/UK type - the benchmark is US pollution intensity, not a carbon price. BUT the fee is reduced for goods from a "partner country" under an international partnership agreement meeting the conditions in ss. 201-202 of the bill, which is the closest analogue and a materially different legal route.</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Not specified in the discussion draft.</t>
+          <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>Not specified in the discussion draft.</t>
+          <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>Fee based on the emissions intensity of the imported good relative to a US benchmark for that good.</t>
+          <t>Fee determined by the amount by which the pollution intensity of the imported product exceeds the US baseline pollution intensity for that product, doubled for non-market economies, and reduced under any applicable partnership agreement.</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>Not specified.</t>
+          <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>U.S. Senate - Cassidy / Graham, Foreign Pollution Fee Act discussion draft; revised bill introduced April 2025</t>
+          <t>U.S. Senate - S. 1325, Foreign Pollution Fee Act of 2025 (Cassidy, Graham), introduced 8 April 2025</t>
         </is>
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>https://www.cassidy.senate.gov/wp-content/uploads/2024/12/FPF-Discussion-Draft.pdf</t>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325</t>
         </is>
       </c>
       <c r="T8" s="4" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>Introduced April 2025, building on 118th-Congress proposals. Not enacted. A border charge without a domestic carbon price raises different GATT Art. III / Art. XX questions from the EU and UK models.</t>
+          <t>Introduced 8 April 2025, updating a 2023 bill after a public comment period. Not enacted. A border charge with no domestic carbon price raises different GATT Art. III:2 / Art. XX questions from the EU and UK models, and the non-market-economy multiplier raises MFN questions under Art. I:1.</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Clean Competition Act of 2025 (Whitehouse)</t>
+          <t>Clean Competition Act of 2025 (S. 3523, Whitehouse / DelBene)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1300,67 +1300,67 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Unavailable - not enacted as at September 2026.</t>
+          <t>Unavailable - not enacted. Introduced 17 December 2025 as S. 3523 (119th Congress), with companion bill H.R. 6787. Charge on covered primary goods would apply to calendar years beginning after 31 Dec 2025; on finished goods after 31 Dec 2027.</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Apply a carbon charge equally to domestic producers and importers in energy-intensive sectors, based on the carbon intensity of covered goods measured against a sectoral benchmark.</t>
+          <t>Amend the Internal Revenue Code to create a carbon border adjustment based on carbon intensity, applying an equivalent charge to domestic producers and importers in energy-intensive sectors. (S. 3523, long title)</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Carbon intensity of covered goods above a sectoral benchmark.</t>
+          <t>Carbon intensity of covered goods, by reference to facility-level emissions already reported to the EPA, measured against the baseline carbon intensity of the covered national industry for 2025.</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
+          <t>Not separately specified in the bill as introduced.</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Partially - the charge extends to finished goods from 2028 by reference to the covered primary goods that are component parts of them, which is a precursor-style pass-through.</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>NOT an economy-wide carbon tax. Targets energy-intensive sectors: iron &amp; steel, aluminium, cement and certain chemicals (fossil fuels are also referenced in sponsor materials). Applies the identical charge to domestic output and to imports, which is designed to limit national-treatment exposure under GATT Art. III:2 - the main legal distinction from the Foreign Pollution Fee Act.</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>N/A - not linked to an economy-wide domestic carbon price, so no origin carbon-price deduction of the EU/UK type. The bill instead equalises by charging domestic producers on the same basis.</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Not specified in the bill as introduced; baselines are derived from reported facility data rather than published default values.</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
           <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>Not specified in the bill as introduced.</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>NOT an economy-wide carbon tax. Targets steel, aluminium, cement and certain chemicals. Distinctive in applying the identical charge to domestic output and to imports, which is designed to reduce national-treatment exposure under GATT Art. III:2.</t>
-        </is>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>N/A - not linked to an economy-wide domestic carbon price, so no origin carbon-price deduction of the EU/UK type.</t>
-        </is>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>Not specified in the bill as introduced.</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>Not specified in the bill as introduced.</t>
-        </is>
-      </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>Charge starting at USD 60 per tonne, applied to carbon intensity above a benchmark, levied equally on domestic producers and importers.</t>
+          <t>Charge = (carbon intensity of the good less the applicable percentage of the baseline carbon intensity of its covered national industry) x relevant quantity x the cost of pollution. The cost of pollution is reported as starting at USD 60 per tonne. The applicable percentage tightens over time, so the effective baseline falls.</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>Reinvested in domestic industrial decarbonisation programmes and in international efforts to support cleaner manufacturing in developing countries.</t>
+          <t>Reinvested in decarbonisation: 75% to a Domestic Industrial Decarbonization Program administered by the Department of Energy, with the balance including international support for cleaner manufacturing in developing countries.</t>
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>U.S. Senate - Whitehouse, Clean Competition Act of 2025 (reintroduced December 2025)</t>
+          <t>U.S. Senate - S. 3523, Clean Competition Act (Whitehouse, with Blumenthal, Heinrich, Schatz, Welch, Van Hollen); House companion H.R. 6787 (DelBene), introduced 17 December 2025</t>
         </is>
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>https://www.congress.gov/</t>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="U9" s="4" t="inlineStr">
         <is>
-          <t>Reintroduced December 2025 and referred to the Senate Committee on Finance; earliest stage of the legislative process. Symmetric domestic/import treatment is its main design distinction from the Foreign Pollution Fee Act.</t>
+          <t>Introduced 17 December 2025 and referred to the Senate Committee on Finance; earliest stage of the legislative process. The fourth iteration of a bill first introduced in 2022 (S. 4355).</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2190,132 +2190,144 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Sourcing principle</t>
+          <t>Verification status</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Each instrument is anchored to an OFFICIAL primary source wherever one exists (national gazettes, ministry pages, the European Commission, gov.uk/HMRC, CARB, ICAP, WTO Documents Online). Secondary and analytical materials are recorded here rather than cited per row.</t>
+          <t>All instrument rows and source links were re-verified on 7 September 2026. Corrections then made: EU de minimis does not apply to hydrogen or electricity; Serbia rate (EUR 4/tCO2e), 5-tonne threshold, statutory default values and four-group product scope added, hydrogen removed as it is not covered by the import tax; Australia report date (13 Feb 2026), the TEBA-removal recommendation and hydrogen added; both US bills given real bill numbers (S. 1325 and S. 3523) and the Foreign Pollution Fee Act's eight product categories added. Generic placeholder links to congress.gov were replaced with bill-specific URLs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Key secondary source</t>
+          <t>Sourcing principle</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>International Institute for Sustainable Development (IISD), The State of Border Carbon Adjustments 2026 (30 July 2026), used for scope framing, the WTO statement landscape, and initial identification of measures. https://www.iisd.org/publications/report/state-of-border-carbon-adjustments-2026</t>
+          <t>Each instrument is anchored to an OFFICIAL primary source wherever one exists (national gazettes, ministry pages, the European Commission, gov.uk/HMRC, CARB, ICAP, WTO Documents Online). Secondary and analytical materials are recorded here rather than cited per row.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>How to read 'status' vs 'status_simple'</t>
+          <t>Key secondary source</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>'status' uses the detailed controlled vocabulary in the Status_legend tab and is what the dashboard filters on. 'status_simple' collapses that to the three-way In Force / Draft / Conceptual classification for headline display. Both are maintained; do not let them drift apart.</t>
+          <t>International Institute for Sustainable Development (IISD), The State of Border Carbon Adjustments 2026 (30 July 2026), used for scope framing, the WTO statement landscape, and initial identification of measures. https://www.iisd.org/publications/report/state-of-border-carbon-adjustments-2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>How to read the scope columns</t>
+          <t>How to read 'status' vs 'status_simple'</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Scope 1/2/3 labels are a comparability overlay, not the legal test. Each instrument defines 'embedded' or 'embodied' emissions in its own methodology annex, and the UK's 'direct emissions' expressly includes upstream precursors. See the Scope_legend tab before relying on a scope cell in advice.</t>
+          <t>'status' uses the detailed controlled vocabulary in the Status_legend tab and is what the dashboard filters on. 'status_simple' collapses that to the three-way In Force / Draft / Conceptual classification for headline display. Both are maintained; do not let them drift apart.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Unfilled cells</t>
+          <t>How to read the scope columns</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Where a design feature has not been settled or published, the cell reads 'To be determined' (the instrument exists but the feature is undecided) or 'Not specified in published material' (the instrument exists and the feature may be settled but is not publicly documented). 'N/A' means the feature is inapplicable by design. Blank means not yet researched - there should be none.</t>
+          <t>Scope 1/2/3 labels are a comparability overlay, not the legal test. Each instrument defines 'embedded' or 'embodied' emissions in its own methodology annex, and the UK's 'direct emissions' expressly includes upstream precursors. See the Scope_legend tab before relying on a scope cell in advice.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Attribution &amp; independence</t>
+          <t>Unfilled cells</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>This tracker is independently compiled and maintained. It is not affiliated with, or endorsed by, IISD or any government or organisation listed. Where data derives from a specific source, that source is linked.</t>
+          <t>Where a design feature has not been settled or published, the cell reads 'To be determined' (the instrument exists but the feature is undecided) or 'Not specified in published material' (the instrument exists and the feature may be settled but is not publicly documented). 'N/A' means the feature is inapplicable by design. Blank means not yet researched - there should be none.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Trade data (planned)</t>
+          <t>Attribution &amp; independence</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Trade-flow analysis will join sector HS codes (Sectors tab) to import/export data (e.g. BACI/CEPII, UN Comtrade). Not yet built; hs_code is the join key. IISD 2026 uses BACI (CEPII 2026) for its exposure figures.</t>
+          <t>This tracker is independently compiled and maintained. It is not affiliated with, or endorsed by, IISD or any government or organisation listed. Where data derives from a specific source, that source is linked.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>HS codes</t>
+          <t>Trade data (planned)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Recorded at chapter/heading level for orientation. Refine to 6-digit, or to the instrument's exact commodity-code list, before using for trade-flow calculations. Note that the EU and UK annexes list specific codes, not whole chapters.</t>
+          <t>Trade-flow analysis will join sector HS codes (Sectors tab) to import/export data (e.g. BACI/CEPII, UN Comtrade). Not yet built; hs_code is the join key. IISD 2026 uses BACI (CEPII 2026) for its exposure figures.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Update cadence</t>
+          <t>HS codes</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Update the relevant tab(s) when an official development occurs; set last_updated on the affected Instruments row. Each edit is version-tracked in the GitHub repository.</t>
+          <t>Recorded at chapter/heading level for orientation. Refine to 6-digit, or to the instrument's exact commodity-code list, before using for trade-flow calculations. Note that the EU and UK annexes list specific codes, not whole chapters.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Licence note</t>
+          <t>Update cadence</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>If reusing IISD material directly, observe its CC BY-NC-SA 4.0 licence (attribute, non-commercial, share-alike). This is general information, not legal advice.</t>
+          <t>Update the relevant tab(s) when an official development occurs; set last_updated on the affected Instruments row. Each edit is version-tracked in the GitHub repository.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Licence note</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>If reusing IISD material directly, observe its CC BY-NC-SA 4.0 licence (attribute, non-commercial, share-alike). This is general information, not legal advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Known data gaps as at 2026-09-07</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>(1) Serbia: Scope 2/3 treatment, default values and de minimis are not documented in accessible published material - the Official Gazette text should be read directly. (2) UK: default values and methodology unpublished. (3) US bills: product lists in draft form only, not verified against enacted text. (4) Norway: no Norwegian implementing regulation yet - all entries are 'intended alignment'.</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>(1) Serbia: rate, thresholds, statutory default values and product scope now verified, but Scope 2/3 treatment and the reference emission values sit in outstanding bylaws - read the Official Gazette text directly before advising. (2) UK: default values and methodology unpublished; secondary legislation not finalised. (3) US bills: verified against congress.gov text as introduced, but neither is enacted and both may change in committee; HS codes for solar products and batteries are indicative only. (4) Norway: no Norwegian implementing regulation yet - every design entry is intended alignment, not law. (5) Thailand and Chinese Taipei: framework instruments only; nearly every parameter awaits subordinate legislation.</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2345,7 +2357,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HOW TO USE - One row per INSTRUMENT x SECTOR. This long-form table is what the dashboard PIVOTS into the sector-coverage matrix (rows = sectors, columns = instruments). Put HS chapter/heading codes in hs_code (semicolon-separated); refine to 6-digit for the trade-flow tab. Instruments with no defined product list yet (TH-CBAM, TR-CLIM, CA-CONSULT, US-FPFA) intentionally have no rows here - do not invent one.</t>
+          <t>HOW TO USE - One row per INSTRUMENT x SECTOR. This long-form table is what the dashboard PIVOTS into the sector-coverage matrix (rows = sectors, columns = instruments). Put HS chapter/heading codes in hs_code (semicolon-separated); refine to 6-digit for the trade-flow tab. Instruments with no defined product list yet (TH-CBAM, TR-CLIM, CA-CONSULT) intentionally have no rows here - do not invent one.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2634,7 +2646,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Scope 1. Recommended for INITIAL coverage (cement and clinker).</t>
+          <t>Scope 1. Recommended for INITIAL coverage (cement and clinker). Clinker identified as the most exposed commodity.</t>
         </is>
       </c>
     </row>
@@ -2729,22 +2741,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>RS-CIPIT</t>
+          <t>AU-BCA</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2804.10</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Embedded emissions. Mirrors EU CBAM scope.</t>
+          <t>Scope 1. Possible future coverage; listed among second-phase candidates.</t>
         </is>
       </c>
     </row>
@@ -2756,17 +2768,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Fertilizers</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>3102; 3105</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Embedded emissions. Mirrors EU CBAM scope.</t>
+          <t>Embedded emissions net of a reference emission value; EUR 4/tCO2e.</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2790,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Iron &amp; steel</t>
+          <t>Fertilizers</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>72; 73</t>
+          <t>3102; 3105</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Embedded emissions. Mirrors EU CBAM scope.</t>
+          <t>Embedded emissions net of a reference emission value; EUR 4/tCO2e.</t>
         </is>
       </c>
     </row>
@@ -2800,17 +2812,17 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Iron &amp; steel</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>72; 73</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Embedded emissions. Mirrors EU CBAM scope.</t>
+          <t>Embedded emissions net of a reference emission value; EUR 4/tCO2e.</t>
         </is>
       </c>
     </row>
@@ -2822,17 +2834,17 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2804.10</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Embedded emissions. Mirrors EU CBAM scope.</t>
+          <t>Embedded emissions net of a reference emission value; EUR 4/tCO2e.</t>
         </is>
       </c>
     </row>
@@ -2971,130 +2983,306 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>US-CCA</t>
+          <t>US-FPFA</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Iron &amp; steel</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>72; 73</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
+          <t>One of eight categories named in S. 1325; fee benchmarked to US pollution intensity. Bill not enacted.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>US-CCA</t>
+          <t>US-FPFA</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
+          <t>One of eight categories named in S. 1325. Bill not enacted.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>US-CCA</t>
+          <t>US-FPFA</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Iron &amp; steel</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>72; 73</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
+          <t>One of eight categories named in S. 1325. Bill not enacted.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>US-CCA</t>
+          <t>US-FPFA</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chemicals (certain)</t>
+          <t>Fertilizers</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>28; 29 (subset)</t>
+          <t>3102; 3105; 2808; 2814</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
+          <t>One of eight categories named in S. 1325. Bill not enacted.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>TW-TRIAL</t>
+          <t>US-FPFA</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Glass</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Trial declaration only - no charge.</t>
+          <t>One of eight categories named in S. 1325. Not covered by the EU or UK CBAMs.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t>US-FPFA</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>2804.10</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>One of eight categories named in S. 1325. Bill not enacted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>US-FPFA</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Solar products</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>8541.43</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>One of eight categories named in S. 1325. Unique to the US proposal - no other BCA covers solar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>US-FPFA</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Batteries (long-duration storage)</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>8507</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>One of eight categories named in S. 1325. Unique to the US proposal - no other BCA covers batteries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Iron &amp; steel</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>72; 73</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Aluminium</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Chemicals (certain)</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>28; 29 (subset)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>TW-TRIAL</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Trial declaration only - no charge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>TW-TRIAL</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Iron &amp; steel</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>72; 73</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Trial declaration only - no charge.</t>
         </is>
@@ -3207,12 +3395,12 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Replaces the value-based exemption with a 50-tonne mass-based annual de minimis; expected to exempt c.182,000 more importers while still covering 99% of in-scope emissions.</t>
+          <t>Adopted 8 Oct 2025, published in the Official Journal 17 Oct 2025, in force 20 Oct 2025. Replaces the EUR 150-per-consignment exemption with a 50-tonne mass-based annual de minimis (not applicable to hydrogen or electricity).</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=OJ:L_202502083</t>
+          <t>https://eur-lex.europa.eu/eli/reg/2025/2083/oj</t>
         </is>
       </c>
     </row>
@@ -3855,12 +4043,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Recommends a BCA for a select group of high-leakage-risk commodities, starting with cement and clinker. Rules out export BCAs.</t>
+          <t>Released 13 February 2026. Recommends a staged BCA for high-leakage-risk commodities starting with cement and clinker; rules out export rebates; recommends removing TEBA for covered commodities.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://www.dcceew.gov.au/climate-change/emissions-reduction/safeguard-mechanism</t>
+          <t>https://www.dcceew.gov.au/climate-change/publications/carbon-leakage-review</t>
         </is>
       </c>
     </row>
@@ -3887,7 +4075,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://www.dcceew.gov.au/climate-change/emissions-reduction/safeguard-mechanism</t>
+          <t>https://www.dcceew.gov.au/climate-change/emissions-reduction/review-carbon-leakage</t>
         </is>
       </c>
     </row>
@@ -3904,12 +4092,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Two laws adopted: Law on Greenhouse Gas Emissions Tax and Law on the Tax on Imports of Carbon-Intensive Products</t>
+          <t>National Assembly adopts the Law on Greenhouse Gas Emissions Tax and the Law on the Tax on Imports of Carbon-Intensive Products</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Domestic and border carbon pricing introduced as a pair.</t>
+          <t>Domestic and border carbon pricing introduced as a pair, both at EUR 4 per tonne CO2e. Several implementing bylaws still outstanding.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -3936,7 +4124,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Same day as the EU CBAM definitive phase. Electricity excluded from the import tax.</t>
+          <t>Same day as the EU CBAM definitive phase. Covers iron &amp; steel, cement, fertilizers and aluminium; electricity and hydrogen are outside the import tax. First annual return due 31 May 2027.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -4012,17 +4200,17 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Revised Foreign Pollution Fee Act of 2025 introduced by Senators Cassidy and Graham</t>
+          <t>Foreign Pollution Fee Act of 2025 (S. 1325) introduced by Senators Cassidy and Graham</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Builds on 118th-Congress proposals. Not enacted as at September 2026.</t>
+          <t>Introduced 8 April 2025 and referred to the Senate Committee on Finance. Updates the 2023 bill (S. 3198, 118th Congress) after a public comment period. Not enacted as at September 2026.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://www.cassidy.senate.gov/wp-content/uploads/2024/12/FPF-Discussion-Draft.pdf</t>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325</t>
         </is>
       </c>
     </row>
@@ -4039,17 +4227,17 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Clean Competition Act of 2025 reintroduced by Senator Whitehouse; referred to the Senate Committee on Finance</t>
+          <t>Clean Competition Act of 2025 (S. 3523) introduced; referred to the Senate Committee on Finance</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Earliest stage of the legislative process.</t>
+          <t>Introduced 17 December 2025 by Senator Whitehouse with five co-sponsors; companion bill H.R. 6787 introduced in the House by Representative DelBene. Earliest stage of the legislative process.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://www.congress.gov/</t>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523</t>
         </is>
       </c>
     </row>
@@ -4391,7 +4579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4484,7 +4672,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=OJ:L_202502083</t>
+          <t>https://eur-lex.europa.eu/eli/reg/2025/2083/oj</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -4744,7 +4932,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Safeguard Mechanism / Carbon Leakage Review</t>
+          <t>Australia's Carbon Leakage Review report (final report)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -4754,7 +4942,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://www.dcceew.gov.au/climate-change/emissions-reduction/safeguard-mechanism</t>
+          <t>https://www.dcceew.gov.au/climate-change/publications/carbon-leakage-review</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -4766,76 +4954,76 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>RS-CIPIT</t>
+          <t>AU-BCA</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Official Gazette of the Republic of Serbia (legal information system)</t>
+          <t>Carbon Leakage Review - review landing page</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Legislation</t>
+          <t>Official page</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://www.pravno-informacioni-sistem.rs/</t>
+          <t>https://www.dcceew.gov.au/climate-change/emissions-reduction/review-carbon-leakage</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NO-CBAM</t>
+          <t>RS-CIPIT</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Miljodirektoratet - CBAM page</t>
+          <t>Official Gazette of the Republic of Serbia (legal information system)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Regulatory page</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
+          <t>https://www.pravno-informacioni-sistem.rs/</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>US-FPFA</t>
+          <t>RS-CIPIT</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Foreign Pollution Fee Act - discussion draft</t>
+          <t>Green taxes in Serbia - what do you need to know? (rate, thresholds, default values)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Bill (draft)</t>
+          <t>Tax alert (secondary)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://www.cassidy.senate.gov/wp-content/uploads/2024/12/FPF-Discussion-Draft.pdf</t>
+          <t>https://kpmg.com/rs/en/insights/tax-alerts/2025/12/green-taxes-in-serbia-what-do-you-need-to-know.html</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -4847,22 +5035,22 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>US-CCA</t>
+          <t>RS-CIPIT</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Clean Competition Act - bill record</t>
+          <t>Serbia rolls out taxes on GHG emissions and imported carbon-intensive products</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>News (secondary)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://www.congress.gov/</t>
+          <t>https://balkangreenenergynews.com/serbia-rolls-out-taxes-on-greenhouse-gas-emissions-imported-carbon-intensive-products/</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -4874,22 +5062,22 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>TH-CBAM</t>
+          <t>NO-CBAM</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ICAP - Thailand country profile (Draft Climate Change Act)</t>
+          <t>Miljodirektoratet - CBAM page</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Official-adjacent profile</t>
+          <t>Regulatory page</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/ets/thailand</t>
+          <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -4901,22 +5089,22 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>TR-CLIM</t>
+          <t>US-FPFA</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Turkiye adopts landmark climate law, paving the way for a national ETS</t>
+          <t>S. 1325 - Foreign Pollution Fee Act of 2025 (bill record)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>News / legal summary</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -4928,22 +5116,22 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>TW-TRIAL</t>
+          <t>US-FPFA</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ministry of Environment - carbon border adjustment mechanism trial declaration proposal</t>
+          <t>S. 1325 - full bill text as introduced</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Bill text</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325/text</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -4955,25 +5143,214 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>US-FPFA</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Foreign Pollution Fee Act - earlier discussion draft</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Bill (draft)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cassidy.senate.gov/wp-content/uploads/2024/12/FPF-Discussion-Draft.pdf</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>S. 3523 - Clean Competition Act (bill record)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>S. 3523 - full bill text as introduced</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Bill text</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523/text</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>H.R. 6787 - Clean Competition Act (House companion)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.congress.gov/bill/119th-congress/house-bill/6787/text</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>TH-CBAM</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ICAP - Thailand country profile (Draft Climate Change Act)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Official-adjacent profile</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/ets/thailand</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TR-CLIM</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Turkiye adopts landmark climate law, paving the way for a national ETS</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>News / legal summary</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>TW-TRIAL</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Environment - carbon border adjustment mechanism trial declaration proposal</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Announcement</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
           <t>CA-CONSULT</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Exploring border carbon adjustments for Canada</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Consultation</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/department-finance/programs/consultations/2021/border-carbon-adjustments/exploring-border-carbon-adjustments-canada.html</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -5340,7 +5717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5455,7 +5832,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Residual category in the EU and UK to date - near-zero import share.</t>
+          <t>Residual category in the EU and UK to date - near-zero import share. NOT covered by the Serbian import tax. Never subject to the EU 50-tonne de minimis.</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5849,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>EU, Serbia (domestic tax only), Norway. EXCLUDED from the UK CBAM and from the Serbian import tax.</t>
+          <t>EU and Norway. EXCLUDED from the UK CBAM and from the Serbian import tax (Serbia taxes domestic generation instead). Never subject to the EU 50-tonne de minimis.</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5900,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Australia possible-future coverage; expressly EXCLUDED from the UK CBAM.</t>
+          <t>Australia possible-future coverage and a US Foreign Pollution Fee Act category; expressly EXCLUDED from the UK CBAM.</t>
         </is>
       </c>
     </row>
@@ -5541,6 +5918,40 @@
       <c r="C12" s="4" t="inlineStr">
         <is>
           <t>US Clean Competition Act subset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Solar products</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>8541.43</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>US Foreign Pollution Fee Act only. No other BCA covers solar; HS heading indicative, verify against the bill's schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Batteries (long-duration storage)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>8507</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>US Foreign Pollution Fee Act only. No other BCA covers batteries; HS heading indicative, verify against the bill's schedule.</t>
         </is>
       </c>
     </row>

--- a/BCA_tracker_only_BCA.xlsx
+++ b/BCA_tracker_only_BCA.xlsx
@@ -11,13 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sectors" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status_legend" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category_legend" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector_legend" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope_legend" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multilateral" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carbon_price_linkage" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status_legend" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category_legend" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector_legend" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage_legend" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope_legend" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multilateral" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -481,14 +483,17 @@
     <col width="44" customWidth="1" min="11" max="11"/>
     <col width="56" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="46" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
-    <col width="62" customWidth="1" min="16" max="16"/>
-    <col width="44" customWidth="1" min="17" max="17"/>
-    <col width="44" customWidth="1" min="18" max="18"/>
-    <col width="52" customWidth="1" min="19" max="19"/>
-    <col width="13" customWidth="1" min="20" max="20"/>
-    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="58" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="62" customWidth="1" min="17" max="17"/>
+    <col width="58" customWidth="1" min="18" max="18"/>
+    <col width="58" customWidth="1" min="19" max="19"/>
+    <col width="44" customWidth="1" min="20" max="20"/>
+    <col width="44" customWidth="1" min="21" max="21"/>
+    <col width="52" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="60" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
@@ -517,6 +522,9 @@
       <c r="S1" s="2" t="n"/>
       <c r="T1" s="2" t="n"/>
       <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -586,40 +594,55 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
+          <t>Qualifying Carbon Prices</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
           <t>Default Values</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>De Minimis Threshold</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>Review and Appeal</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>Revenue Use</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>primary_source</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>official_url</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>One Line Summary of the Measure</t>
         </is>
@@ -693,40 +716,55 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
+          <t>NO PUBLISHED LIST. Art. 9 allows deduction of a carbon price 'effectively paid' at origin, but the implementing act is still a DRAFT: published 13 May 2026, feedback closed 10 June 2026, member state vote expected September 2026. The draft sets four recognition pathways, caps Paris Art. 6.2/6.4 credits at 10% of the deduction, and creates a new 'independent person' certification role. Free allowances, baseline exemptions, tax rebates and indirect cost compensation all REDUCE the price counted as effectively paid. The Commission may publish default carbon prices per third country. The draft would apply retroactively from 1 Jan 2026. Contrast the UK, which has already published a list.</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
           <t>YES - country- and product-specific default values adopted by implementing/delegated acts (Nov-Dec 2025). Markup on default values: 10% (2026), 20% (2027), 30% (from 2028); fertilizers 1%.</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>50 tonnes of imported CBAM goods per importer per year (cumulative net mass). IMPORTANT: the threshold does NOT apply to hydrogen or electricity, which remain in scope at any volume. Introduced by Reg (EU) 2025/2083, replacing the earlier EUR 150-per-consignment exemption. Expected to exempt c.182,000 additional importers while still covering 99% of in-scope emissions.</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Number of CBAM certificates = embedded emissions, reduced by the free-allocation adjustment factor and by the effective carbon price paid at origin. Certificate price: 2026 = quarterly average of EU ETS closing prices for the quarter of importation; from 2027 = weekly average of EU ETS auction closing prices. Surrender obligation phases in with the EU ETS free-allowance phase-out (2.5% of emissions in 2026 rising to 100% in 2034). First published quarterly price: EUR 75.36/tCO2e (7 April 2026).</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Actual emissions must be verified by a verifier accredited by an EU/EEA National Accreditation Body under Reg (EC) 765/2008. Accreditation conditions: Delegated Reg (EU) 2025/2551. Verification rules: Implementing Reg (EU) 2025/2546 - risk-based, REASONABLE ASSURANCE standard, with site visits; the report records a satisfactory or unsatisfactory opinion. Verifiers must register in the CBAM Registry within two months of accreditation but not before 1 Sept 2026, and issue verification reports in the Registry from Jan 2027. First accreditations expected around Sept 2026; Commission guidance for verifiers and NABs published 24 Aug 2026. Reports may be reviewed by the Commission and by National Competent Authorities. NABs are peer-evaluated by European co-operation for Accreditation.</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>Administered by MEMBER STATE National Competent Authorities, not the Commission. Refusal or revocation of authorised CBAM declarant status carries a right of appeal under national law, and the NCA must register the existence and outcome of the appeal in the CBAM Registry (Implementing Reg (EU) 2025/486). An appeal does NOT suspend a revocation decision. Substantive challenges run through member state administrative and judicial review, with a possible preliminary reference to the CJEU under TFEU Art. 267 - so the practical remedy varies by member state of import.</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>General budget of the EU and of EU member states. A separate legislative proposal would create a 2-year Temporary Decarbonisation Fund allocating 25% of CBAM revenues in 2028-2029 to EU energy-intensive industry.</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>European Commission - Regulation (EU) 2023/956 as amended by Regulation (EU) 2025/2083</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr">
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>https://taxation-customs.ec.europa.eu/carbon-border-adjustment-mechanism_en</t>
         </is>
       </c>
-      <c r="T3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>World's first ETS-based BCA in force. First declaration and payment fall due 30 September 2027 for 2026 imports.</t>
         </is>
@@ -790,7 +828,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Electricity is NOT covered (unlike the EU CBAM). Glass and ceramics expressly excluded. Government to publish a call for evidence on the fuel sector and is considering whether to include refined fuel products in future.</t>
+          <t>Electricity is NOT covered (unlike the EU CBAM). Glass and ceramics expressly excluded. Certain SCRAP products within the aluminium and iron &amp; steel sectors are excluded by commodity code. Goods imported other than in the course of business are out of scope. Government to publish a call for evidence on the fuel sector and is considering whether to include refined fuel products in future.</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -800,42 +838,57 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>YES - reporting on default values permitted; from 2027 a single default value per product will apply. Values and the underlying methodology had not been published as at September 2026 and may be subject to further consultation.</t>
+          <t>YES - HMRC published a list of 16 Qualifying Carbon Pricing Schemes on 27 Aug 2026 (assessed as at 19 June 2026), the first such list published by any BCA. Criteria are in SI 2026/809. The list is expressly NON-EXHAUSTIVE: unlisted schemes may still qualify, regional schemes are under review, and HMRC invites submissions. Emissions covered by FREE ALLOWANCES do not qualify, because no effective carbon price was paid; rebates and refunds reduce relief; in some cases no relief is available at all. The liable person, not HMRC, is responsible for determining eligibility. See the Carbon_price_linkage tab for the full list.</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
+          <t>YES - reporting on default values permitted; from 2027 a single default value per product will apply. Values and methodology STILL UNPUBLISHED as at Sept 2026; the draft Emissions and Verification Regulations remain outstanding.</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
           <t>GBP 50,000 of imports by value over a rolling 12-month period.</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Structured as a TAX collected by HMRC through direct-tax channels, not as tradable certificates. The rate is set separately for each CBAM sector, reflecting the UK ETS price adjusted for the free allocation granted to that sector and a sectoral reduction factor updated annually as free allowances are phased out; adjusted quarterly. Liability is reduced by any deductible overseas carbon price.</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>Emissions and Verification Regulations were still DRAFT as at Sept 2026, and default values remain unpublished. For carbon price relief, reg 9 of SI 2026/809 requires the importer to obtain a 'carbon pricing verification form' completed by a verifier and provided by that verifier to the installation that manufactured the good, in a form published by HMRC. Importers may use independently verified actual emissions or default values. Records supporting a relief claim must be kept for SIX YEARS from the day after the end of the accounting period covered by the return.</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>HMRC administers UK CBAM as a TAX, so disputes follow ordinary UK tax procedure: HMRC statutory review, then appeal to the First-tier Tribunal (Tax Chamber) - not the customs or environmental enforcement routes that apply under the EU CBAM. This is the single clearest procedural divergence between the two mechanisms and matters for forum and timing. Existing HMRC penalty regimes apply, with specifics to be confirmed.</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>General budget.</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>HM Revenue &amp; Customs and HM Treasury - Carbon Border Adjustment Mechanism (CBAM): policy summary (2026)</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>HM Revenue &amp; Customs and HM Treasury - CBAM policy summary (updated 16 July 2026); SI 2026/809 (rate calculation and carbon price relief), made 13 July 2026</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
         <is>
           <t>https://www.gov.uk/government/publications/carbon-border-adjustment-mechanism-cbam-policy-summary</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>Four draft statutory instruments consulted on in 2026 (consultations closed 24 March and 21 May); secondary legislation to be finalised before commencement. EU-UK ETS linkage under negotiation and could relieve bilateral trade from both CBAMs.</t>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>Operational rulebook largely complete: SI 2026/802, 809 and 830 were made 13-14 July 2026, in force 1 Jan 2027. Emissions and verification rules remain draft and default values unpublished. EU-UK ETS linkage under negotiation and could relieve bilateral trade from both CBAMs.</t>
         </is>
       </c>
     </row>
@@ -907,40 +960,55 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
+          <t>Recommended approach only: EXPLICIT carbon prices, credited by reference to the difference between the effective explicit carbon price in the country of origin and the Australian benchmark price. No list of qualifying schemes exists, and none can until the measure is adopted. Note that Australia's own Safeguard Mechanism appears on the UK's qualifying list.</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
           <t>RECOMMENDED - the review recommends 'suitable default emissions intensity values' aligned to emerging international standards while minimising administrative burden. No values published.</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>Not specified in the final report.</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Liability calculated by reference to (a) emissions above the Safeguard Mechanism emissions-intensity baseline, and (b) the difference between the effective explicit carbon price in the country of origin and the Australian benchmark price. Because the Safeguard Mechanism charges only emissions above a baseline, imports at or below the baseline would face no liability.</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>Not designed. The review recommends default emissions intensity values aligned to emerging international standards in order to minimise administrative burden, which implies a lighter-touch model than the EU's accredited-verifier architecture, but no verification regime has been specified.</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>Not designed. The review did not address importer review or appeal rights. If a BCA were built onto the Safeguard Mechanism, the Clean Energy Regulator's existing NGER administrative framework would be the natural host, but nothing has been proposed - do not rely on any assumed route.</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>Recommended to be channelled to support implementation and industrial decarbonisation objectives in developing trade-partner countries.</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water - Carbon Leakage Review, final report (released 13 February 2026; review conducted July 2023 - March 2025)</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>https://www.dcceew.gov.au/climate-change/publications/carbon-leakage-review</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>A recommendation of an independent review, NOT government policy. Initial coverage cement and clinker; lime, hydrogen, ammonia and derivatives, iron &amp; steel and glass flagged as possible future additions. Clinker was identified as the most exposed commodity.</t>
         </is>
@@ -1014,40 +1082,55 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
+          <t>No published list. Liability is reduced where an emissions charge has already been paid in the country of origin, on submission of appropriate evidence, but the law does not name qualifying schemes and the assessing methodology sits in outstanding bylaws. Note that Serbia's own carbon tax appears on the UK's qualifying list.</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
           <t>YES - default values are provided in the legislation. Importers may instead report independently verified actual emissions; verification must be carried out by bodies accredited under the International Accreditation Forum (IAF) system.</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>Importers of fewer than 5 tonnes of a covered product in a calendar year are not taxpayers. Note this is far tighter than the EU threshold (50 tonnes).</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Tax base = actual or default embedded emissions of the imported product, reduced by prescribed reference emission values, taxed at EUR 4 per tonne CO2e (converted to dinars at the National Bank of Serbia middle rate on the last day of the tax period). Liability is reduced by any emissions charge already paid at origin. Annual return due 31 May for the preceding year. The EUR 4 rate is roughly 5% of the Q1 2026 EU CBAM certificate price of EUR 75.36.</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>Importers may report independently verified actual emissions or use the statutory default values. Verification must be carried out by bodies accredited under the INTERNATIONAL ACCREDITATION FORUM (IAF) system - a materially different anchor from the EU's National Accreditation Body route, and one that may admit a wider pool of verifiers.</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>NOT SPECIFIED in either law as published. General Serbian tax-procedure rights - objection to the Tax Administration, then administrative court - would ordinarily apply, but the carbon legislation is silent and several implementing bylaws were outstanding at adoption. Read the Official Gazette text directly before advising a client on remedies.</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>Not specified in the law. The companion GHG Emissions Tax offers electricity producers a 20% tax credit for eligible decarbonisation investment, capped at 80% of liability.</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="U6" s="4" t="inlineStr">
         <is>
           <t>Official Gazette of the Republic of Serbia - Law on the Tax on Imports of Carbon-Intensive Products (adopted by the National Assembly, December 2025)</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>https://www.pravno-informacioni-sistem.rs/</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>The second BCA in the world to enter into force, at EUR 4/tCO2e. Adopted as one of a pair with the domestic Law on Greenhouse Gas Emissions Tax; Serbia is among the most EU CBAM-exposed economies (7.1% of its global exports). Several implementing bylaws were still outstanding at adoption.</t>
         </is>
@@ -1121,40 +1204,55 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
+          <t>Intended to follow the EU's Art. 9 regime once the CBAM Regulation is incorporated into the EEA Agreement. Nothing adopted in Norwegian law, and the EU act on which it would depend is itself still a draft.</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
           <t>Intended to align with the EU CBAM. Not yet published.</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>Intended to align with the EU CBAM (50 tonnes per year). Not yet confirmed.</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Intended to follow the EU CBAM methodology in full.</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>Intended alignment with the EU model (accredited verifiers, reasonable assurance). No Norwegian implementing regulation adopted.</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>Not yet established. Would be expected to follow Norwegian administrative appeal procedure once regulations are adopted, but nothing is specified.</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>Not specified.</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t>Norwegian Environment Agency (Miljodirektoratet) - CBAM: justering av karbonpris for import av varer til EOS (2026)</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>Treat the 2027 date as a target, not a legal commencement date - the EEA incorporation step is the binding constraint. Norwegian goods are already exempt from the EU CBAM through the EU-EEA ETS relationship.</t>
         </is>
@@ -1228,40 +1326,55 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
+          <t>NO carbon-price recognition mechanism. The bill instead reduces the fee for goods from a 'partner country' under an international partnership agreement satisfying ss. 201-202. No such agreement exists. A 2x multiplier applies to covered products from non-market economies, which cuts the opposite way.</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
           <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Fee determined by the amount by which the pollution intensity of the imported product exceeds the US baseline pollution intensity for that product, doubled for non-market economies, and reduced under any applicable partnership agreement.</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>Not specified in the bill as introduced. Pollution intensity is determined against US benchmarks, with GHGs measured as CO2e on a 100-year GWP basis per 40 CFR Part 98 subpart A table A-1. The bill does not establish an accreditation or third-party verification regime of the EU/UK type.</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>Not specified in the bill as introduced. The bill gives the Secretary of Commerce anti-evasion powers, including prohibiting imports from an evading country or producer, but sets out no importer-facing review or appeal route against an intensity determination.</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>U.S. Senate - S. 1325, Foreign Pollution Fee Act of 2025 (Cassidy, Graham), introduced 8 April 2025</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>Introduced 8 April 2025, updating a 2023 bill after a public comment period. Not enacted. A border charge with no domestic carbon price raises different GATT Art. III:2 / Art. XX questions from the EU and UK models, and the non-market-economy multiplier raises MFN questions under Art. I:1.</t>
         </is>
@@ -1335,40 +1448,55 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
+          <t>N/A - there is no origin carbon-price deduction, because the charge falls equally on domestic producers and importers. Equalisation is achieved by charging domestic output on the same basis rather than by crediting foreign prices.</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
           <t>Not specified in the bill as introduced; baselines are derived from reported facility data rather than published default values.</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Charge = (carbon intensity of the good less the applicable percentage of the baseline carbon intensity of its covered national industry) x relevant quantity x the cost of pollution. The cost of pollution is reported as starting at USD 60 per tonne. The applicable percentage tightens over time, so the effective baseline falls.</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>For domestic producers the charge builds on facility-level emissions already reported to the EPA. For imports the bill relies on reported carbon intensity measured against the 2025 baseline for the covered national industry; no separate accreditation regime is established in the bill as introduced.</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>Not specified in the bill as introduced. Because the measure would amend the Internal Revenue Code, ordinary US tax assessment, refund and Tax Court procedures would be the natural route, but the bill does not address this.</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>Reinvested in decarbonisation: 75% to a Domestic Industrial Decarbonization Program administered by the Department of Energy, with the balance including international support for cleaner manufacturing in developing countries.</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="U9" s="4" t="inlineStr">
         <is>
           <t>U.S. Senate - S. 3523, Clean Competition Act (Whitehouse, with Blumenthal, Heinrich, Schatz, Welch, Van Hollen); House companion H.R. 6787 (DelBene), introduced 17 December 2025</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr">
+      <c r="W9" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr">
+      <c r="X9" s="4" t="inlineStr">
         <is>
           <t>Introduced 17 December 2025 and referred to the Senate Committee on Finance; earliest stage of the legislative process. The fourth iteration of a bill first introduced in 2022 (S. 4355).</t>
         </is>
@@ -1442,40 +1570,55 @@
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
+          <t>To be determined by ministerial regulation. The draft Act provides the framework only.</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
           <t>To be determined - not specified in the draft Act.</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>To be determined - not specified in the draft Act.</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr">
+      <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>To be determined by ministerial regulation. The draft Act provides the enabling framework only.</t>
         </is>
       </c>
-      <c r="Q10" s="5" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>To be determined. The draft Act's ETS and carbon-tax components envisage MRV infrastructure administered by the Department of Climate Change and Environment, but no CBAM-specific verification or assurance standard is specified.</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>To be determined by ministerial regulation. No importer review or appeal route appears in the draft Act.</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr">
         <is>
           <t>Climate Fund - the draft Act establishes a Climate Fund financed in part by ETS and CBAM revenues, constituted as a juristic person and non-ministerial state agency.</t>
         </is>
       </c>
-      <c r="R10" s="5" t="inlineStr">
+      <c r="U10" s="5" t="inlineStr">
         <is>
           <t>ICAP - Thailand; Draft Climate Change Act approved by Cabinet 2 December 2025</t>
         </is>
       </c>
-      <c r="S10" s="5" t="inlineStr">
+      <c r="V10" s="5" t="inlineStr">
         <is>
           <t>https://icapcarbonaction.com/en/ets/thailand</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr">
+      <c r="W10" s="5" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U10" s="5" t="inlineStr">
+      <c r="X10" s="5" t="inlineStr">
         <is>
           <t>ADDED 2026-09. The first Asian CBAM to reach draft-legislation stage. Cabinet-approved 2 Dec 2025; third public hearing completed 8 April 2026; before the Office of the Council of State and Parliament.</t>
         </is>
@@ -1549,40 +1692,55 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
+          <t>To be determined - no CBAM has been designed, so no recognition regime exists.</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
           <t>To be determined.</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>To be determined.</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>To be determined by implementing legislation. No mechanism has been designed as at September 2026.</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>To be determined. The Climate Law establishes a Carbon Market Board and an MRV framework for the national ETS; any CBAM verification architecture would follow from implementing legislation.</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>To be determined. No CBAM assessment exists to dispute.</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>Not specified.</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>Climate Law No. 7552, Official Gazette of 9 July 2025 No. 32951; ICAP - Turkiye adopts landmark climate law (2025)</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="W11" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr">
+      <c r="X11" s="4" t="inlineStr">
         <is>
           <t>ENABLING PROVISION ONLY - no Turkish CBAM has been designed. Turkiye is the second-largest source of EU CBAM-covered imports (11.4% in 2024) and among the most exposed EU trading partners.</t>
         </is>
@@ -1656,40 +1814,55 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
+          <t>To be determined. Note that Chinese Taipei's own carbon fee appears on the UK's qualifying list.</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
           <t>To be determined.</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>To be determined.</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>Trial reporting only at this stage; no charge. The underlying legal framework is still being finalised.</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>Trial declaration only. Importers of cement and steel would report carbon emissions data; no charge, and no verification or assurance standard has been set.</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>To be determined. There is no charge at the trial stage, so there is no assessment to dispute.</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>Not specified.</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="U12" s="4" t="inlineStr">
         <is>
           <t>Ministry of Environment - proposal for a carbon border adjustment mechanism beginning with a trial declaration system (2025); Climate Change Response Act 2023</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr">
+      <c r="V12" s="4" t="inlineStr">
         <is>
           <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="W12" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
+      <c r="X12" s="4" t="inlineStr">
         <is>
           <t>Already present in the pilot dataset but previously near-empty; now populated. Legal basis in the Climate Change Response Act 2023. A declaration trial, not a charging mechanism.</t>
         </is>
@@ -1763,40 +1936,55 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
+          <t>N/A - no design was produced. Note that Canada's Federal OBPS appears on the UK's qualifying list.</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
           <t>N/A - no design was produced.</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>N/A - no design was produced.</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>N/A - no design was produced.</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>N/A - no design was produced.</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>N/A - no design was produced.</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>N/A - no design was produced.</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
         <is>
           <t>Government of Canada, Department of Finance - Exploring border carbon adjustments for Canada (2021)</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/department-finance/programs/consultations/2021/border-carbon-adjustments/exploring-border-carbon-adjustments-canada.html</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="W13" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="X13" s="4" t="inlineStr">
         <is>
           <t>Dormant. Canada's industrial carbon price was significantly weakened in May 2026, reducing the leakage pressure that would otherwise motivate a BCA. Category corrected from 'BCA' to 'Proposal'.</t>
         </is>
@@ -1804,13 +1992,505 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A1:X1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="76" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>REFERENCE - Taxonomy for the Scope 1 / 2 / 3 columns in the Instruments tab, requested in the pilot dataset. IMPORTANT: these labels are a COMPARABILITY OVERLAY, not the legal test. Each instrument defines 'embedded' or 'embodied' emissions in its own methodology annex. Read this tab before relying on a scope cell in advice.</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>scope_term</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>definition</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>how BCAs currently treat it</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>authority</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Scope 1</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Direct greenhouse gas emissions from sources owned or controlled by the producing installation - e.g. fuel combustion in a kiln or blast furnace, and process emissions such as calcination in cement production.</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Covered by every BCA in this tracker. It is the common denominator across the EU, UK, Serbian, Australian and Californian measures.</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>GHG Protocol Corporate Standard; Reg (EU) 2023/956 Annex IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Scope 2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Indirect emissions from generation of purchased electricity, steam, heating or cooling consumed by the installation.</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>EU CBAM: cement and fertilizers only. UK CBAM: deferred to 2029 at the earliest. Australia: not recommended. This is the single largest design divergence between the EU and UK mechanisms.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>GHG Protocol Corporate Standard; Reg (EU) 2023/956 Annex IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Scope 3 (upstream, precursors only)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Emissions embedded in specified input goods (precursors) that are themselves within the mechanism's product scope - not full value-chain Scope 3.</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>EU CBAM: listed precursors only. UK CBAM: systematically includes upstream precursor emissions, which is why UK coverage is described as broader on Scope 3 than the EU's.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Reg (EU) 2023/956 Annex IV; HMRC/HM Treasury CBAM policy summary (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Scope 3 (full value chain)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>All other indirect emissions across the upstream and downstream value chain, including transport, distribution and use of sold products.</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>NOT covered by any BCA currently in force or in draft. Occasionally raised in modelling studies (e.g. semiconductor exposure analyses) but not in any legal instrument.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>GHG Protocol Corporate Value Chain (Scope 3) Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Embedded / embodied emissions</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>The operative legal term in most BCA instruments. Defined by each instrument's own methodology rather than by the GHG Protocol scopes, and usually equates to Scope 1 plus a defined subset of Scope 2 and precursor Scope 3.</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Use the instrument's own definition when advising. The tracker maps each instrument onto the Scope 1/2/3 vocabulary for comparability, but the legal test is the instrument's own methodology annex.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Reg (EU) 2023/956 Art. 3 and Annex IV; UK CBAM draft secondary legislation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Direct emissions (UK usage)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>The UK CBAM's term for emissions in scope: direct emissions embodied in imported goods, including those embodied in CBAM-covered precursor goods.</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Note the terminological trap: the UK's 'direct emissions' expressly INCLUDES upstream precursor (Scope 3) emissions, so it is not equivalent to Scope 1.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>HM Revenue &amp; Customs / HM Treasury - CBAM policy summary (2026)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>REFERENCE - Jurisdictions checked during the September 2026 sweep that do NOT (yet) have a BCA instrument, and so have no row in the Instruments tab. Recorded so the negative finding is auditable and so nobody re-researches them. Promote a row to the Instruments tab only when a primary source shows an actual proposal or instrument.</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>jurisdiction</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>what exists now</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>why it is on the watchlist</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Considered and declined</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Government decided against introducing a CBAM parallel to the EU's, in a report published June 2023. Swiss-origin goods are exempt from the EU CBAM because the Swiss and EU emissions trading systems are linked.</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Monitor only. A reversal would most likely follow from changes to the EU-Switzerland ETS link.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/news/swiss-ets-reform-comes-force</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Domestic pricing in development</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Draft ETS law released for public consultation 15 May 2026. Compliance obligation would rise from 10% in 2028 to 100% in 2034, explicitly mirroring the EU CBAM phase-in. No Ukrainian BCA proposed.</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>High relevance: Ukraine is among the most EU CBAM-exposed economies (8.1% of global exports). Parliament has been asked to seek a CBAM exemption.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/news/ukraine-releases-draft-ets-law-consultations</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Republic of Korea</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Domestic pricing only</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>K-ETS operating since 2015 and covering c.73-79% of national emissions. Fourth phase reforms from 2026. No Korean BCA proposed.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Watch as the most advanced candidate for an EU CBAM Art. 9 origin carbon-price deduction. No jurisdiction had received formal Commission confirmation as at April 2026.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/ets/korea-emissions-trading-scheme</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Domestic pricing only</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>GX framework and phased carbon pricing. No BCA proposed. Active at the WTO on interoperability and non-binding measurement guidance.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Identified in academic work as a likely future adopter if the EU CBAM broadens. Co-sponsor of WT/CTE/W/269/Rev.5 on measurement methodologies.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/ets/japan-tokyo-cap-and-trade-program</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Domestic pricing only</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>SBCE (Sistema Brasileiro de Comercio de Emissoes) established by federal law in December 2024; rules still being finalised. No Brazilian BCA proposed.</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Watch for Art. 9 deduction eligibility. Hosted COP 30 and launched the Integrated Forum on Climate Change and Trade.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/ets/brazil</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Domestic pricing only; opposed to BCAs</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Carbon Credit Trading Scheme (CCTS) under the Bureau of Energy Efficiency. No Indian BCA proposed. India has been among the most vocal WTO critics of the EU CBAM.</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Highest-priority watch item: the EU-India FTA (concluded Jan 2026) contains the first dedicated CBAM annex (Annex 14-A), a likely template for future agreements.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>https://beeindia.gov.in/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Domestic pricing only</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>National ETS expanded in March 2025 to cover steel, cement and aluminium - the CBAM-targeted sectors. No Chinese BCA proposed.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Largest single source of EU CBAM-covered imports (16.9% in 2024). Has tabled a WTO submission on carbon-standards fragmentation (G/TBT/W/818).</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/ets/china-national-ets</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Conceptual - external advice only</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Investment, Trade and Industry has been advised to consider a Malaysian CBAM with a pilot in the steel sector. No government proposal identified.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Low confidence: the source is external advice, not a government position. Do not promote to the Instruments tab without a primary source.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>https://zerocarbon-analytics.org/finance/carbon-border-adjustment-mechanisms-require-coordinated-global-action/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Opposed; WTO dispute</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>No BCA. Filed a WTO request for consultations against the EU in May 2025 concerning the CBAM and aspects of the EU ETS. No further procedural steps taken at the time of the IISD 2026 report.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Watch the dispute docket - the first WTO challenge to a BCA.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.iisd.org/publications/report/state-of-border-carbon-adjustments-2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2142,13 +2822,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2190,142 +2870,166 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Verification status</t>
+          <t>Third-country carbon price linkage</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>All instrument rows and source links were re-verified on 7 September 2026. Corrections then made: EU de minimis does not apply to hydrogen or electricity; Serbia rate (EUR 4/tCO2e), 5-tonne threshold, statutory default values and four-group product scope added, hydrogen removed as it is not covered by the import tax; Australia report date (13 Feb 2026), the TEBA-removal recommendation and hydrogen added; both US bills given real bill numbers (S. 1325 and S. 3523) and the Foreign Pollution Fee Act's eight product categories added. Generic placeholder links to congress.gov were replaced with bill-specific URLs.</t>
+          <t>The Carbon_price_linkage tab records which foreign carbon pricing schemes each instrument recognises. As at Sept 2026 only the UK has published a list (16 schemes, 27 Aug 2026). The EU's Art. 9 implementing act remains a draft, so no EU list exists and importers in the definitive phase are already incurring obligations without settled deduction rules. Treat the UK list as the only authoritative recognition list currently in existence, and note it is expressly non-exhaustive.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Sourcing principle</t>
+          <t>Verification and appeal routes</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Each instrument is anchored to an OFFICIAL primary source wherever one exists (national gazettes, ministry pages, the European Commission, gov.uk/HMRC, CARB, ICAP, WTO Documents Online). Secondary and analytical materials are recorded here rather than cited per row.</t>
+          <t>Two new columns record who verifies emissions and what an importer does when it disagrees with an assessment. The routes differ sharply: the EU runs on accredited verifiers supervised by member state National Accreditation Bodies with appeals through member state administrative and judicial review (and possible CJEU reference), while the UK administers CBAM as a tax with HMRC statutory review and appeal to the First-tier Tribunal (Tax Chamber). Serbia anchors verification to IAF accreditation instead. Several instruments have no appeal route at all because they are not yet law - those cells say so rather than guessing.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Key secondary source</t>
+          <t>Verification status</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>International Institute for Sustainable Development (IISD), The State of Border Carbon Adjustments 2026 (30 July 2026), used for scope framing, the WTO statement landscape, and initial identification of measures. https://www.iisd.org/publications/report/state-of-border-carbon-adjustments-2026</t>
+          <t>All instrument rows and source links were re-verified on 7 September 2026, and again on 9 September 2026 for verification, appeal and carbon-price-linkage content. Corrections then made: EU de minimis does not apply to hydrogen or electricity; Serbia rate (EUR 4/tCO2e), 5-tonne threshold, statutory default values and four-group product scope added, hydrogen removed as it is not covered by the import tax; Australia report date (13 Feb 2026), the TEBA-removal recommendation and hydrogen added; both US bills given real bill numbers (S. 1325 and S. 3523) and the Foreign Pollution Fee Act's eight product categories added. Generic placeholder links to congress.gov were replaced with bill-specific URLs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>How to read 'status' vs 'status_simple'</t>
+          <t>Sourcing principle</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>'status' uses the detailed controlled vocabulary in the Status_legend tab and is what the dashboard filters on. 'status_simple' collapses that to the three-way In Force / Draft / Conceptual classification for headline display. Both are maintained; do not let them drift apart.</t>
+          <t>Each instrument is anchored to an OFFICIAL primary source wherever one exists (national gazettes, ministry pages, the European Commission, gov.uk/HMRC, CARB, ICAP, WTO Documents Online). Secondary and analytical materials are recorded here rather than cited per row.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>How to read the scope columns</t>
+          <t>Key secondary source</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Scope 1/2/3 labels are a comparability overlay, not the legal test. Each instrument defines 'embedded' or 'embodied' emissions in its own methodology annex, and the UK's 'direct emissions' expressly includes upstream precursors. See the Scope_legend tab before relying on a scope cell in advice.</t>
+          <t>International Institute for Sustainable Development (IISD), The State of Border Carbon Adjustments 2026 (30 July 2026), used for scope framing, the WTO statement landscape, and initial identification of measures. https://www.iisd.org/publications/report/state-of-border-carbon-adjustments-2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Unfilled cells</t>
+          <t>How to read 'status' vs 'status_simple'</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Where a design feature has not been settled or published, the cell reads 'To be determined' (the instrument exists but the feature is undecided) or 'Not specified in published material' (the instrument exists and the feature may be settled but is not publicly documented). 'N/A' means the feature is inapplicable by design. Blank means not yet researched - there should be none.</t>
+          <t>'status' uses the detailed controlled vocabulary in the Status_legend tab and is what the dashboard filters on. 'status_simple' collapses that to the three-way In Force / Draft / Conceptual classification for headline display. Both are maintained; do not let them drift apart.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Attribution &amp; independence</t>
+          <t>How to read the scope columns</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>This tracker is independently compiled and maintained. It is not affiliated with, or endorsed by, IISD or any government or organisation listed. Where data derives from a specific source, that source is linked.</t>
+          <t>Scope 1/2/3 labels are a comparability overlay, not the legal test. Each instrument defines 'embedded' or 'embodied' emissions in its own methodology annex, and the UK's 'direct emissions' expressly includes upstream precursors. See the Scope_legend tab before relying on a scope cell in advice.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Trade data (planned)</t>
+          <t>Unfilled cells</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Trade-flow analysis will join sector HS codes (Sectors tab) to import/export data (e.g. BACI/CEPII, UN Comtrade). Not yet built; hs_code is the join key. IISD 2026 uses BACI (CEPII 2026) for its exposure figures.</t>
+          <t>Where a design feature has not been settled or published, the cell reads 'To be determined' (the instrument exists but the feature is undecided) or 'Not specified in published material' (the instrument exists and the feature may be settled but is not publicly documented). 'N/A' means the feature is inapplicable by design. Blank means not yet researched - there should be none.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>HS codes</t>
+          <t>Attribution &amp; independence</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Recorded at chapter/heading level for orientation. Refine to 6-digit, or to the instrument's exact commodity-code list, before using for trade-flow calculations. Note that the EU and UK annexes list specific codes, not whole chapters.</t>
+          <t>This tracker is independently compiled and maintained. It is not affiliated with, or endorsed by, IISD or any government or organisation listed. Where data derives from a specific source, that source is linked.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Update cadence</t>
+          <t>Trade data (planned)</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Update the relevant tab(s) when an official development occurs; set last_updated on the affected Instruments row. Each edit is version-tracked in the GitHub repository.</t>
+          <t>Trade-flow analysis will join sector HS codes (Sectors tab) to import/export data (e.g. BACI/CEPII, UN Comtrade). Not yet built; hs_code is the join key. IISD 2026 uses BACI (CEPII 2026) for its exposure figures.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Licence note</t>
+          <t>HS codes</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>If reusing IISD material directly, observe its CC BY-NC-SA 4.0 licence (attribute, non-commercial, share-alike). This is general information, not legal advice.</t>
+          <t>Recorded at chapter/heading level for orientation. Refine to 6-digit, or to the instrument's exact commodity-code list, before using for trade-flow calculations. Note that the EU and UK annexes list specific codes, not whole chapters.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>Update cadence</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Update the relevant tab(s) when an official development occurs; set last_updated on the affected Instruments row. Each edit is version-tracked in the GitHub repository.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Licence note</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>If reusing IISD material directly, observe its CC BY-NC-SA 4.0 licence (attribute, non-commercial, share-alike). This is general information, not legal advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Known data gaps as at 2026-09-07</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(1) Serbia: rate, thresholds, statutory default values and product scope now verified, but Scope 2/3 treatment and the reference emission values sit in outstanding bylaws - read the Official Gazette text directly before advising. (2) UK: default values and methodology unpublished; secondary legislation not finalised. (3) US bills: verified against congress.gov text as introduced, but neither is enacted and both may change in committee; HS codes for solar products and batteries are indicative only. (4) Norway: no Norwegian implementing regulation yet - every design entry is intended alignment, not law. (5) Thailand and Chinese Taipei: framework instruments only; nearly every parameter awaits subordinate legislation.</t>
         </is>
@@ -2345,24 +3049,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="82" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HOW TO USE - One row per INSTRUMENT x SECTOR. This long-form table is what the dashboard PIVOTS into the sector-coverage matrix (rows = sectors, columns = instruments). Put HS chapter/heading codes in hs_code (semicolon-separated); refine to 6-digit for the trade-flow tab. Instruments with no defined product list yet (TH-CBAM, TR-CLIM, CA-CONSULT) intentionally have no rows here - do not invent one.</t>
+          <t>HOW TO USE - One row per INSTRUMENT x SECTOR. This long-form table is what the dashboard PIVOTS into the sector-coverage matrix. THE 'coverage' COLUMN IS LOAD-BEARING: 'Current scope' = the sector is within the instrument's defined scope; 'Prospective' = officially flagged for possible future addition but NOT in scope today. See the Coverage_legend tab. Read coverage together with the instrument's status - Australia's cement row is 'Current scope' but the instrument is only a recommendation. Put HS chapter/heading codes in hs_code (semicolon-separated); refine to 6-digit for the trade-flow tab, and never use a Prospective row's codes for trade-flow work. Instruments with no defined product list yet (TH-CBAM, TR-CLIM, CA-CONSULT) intentionally have no rows here - do not invent one.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -2377,10 +3083,15 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>coverage</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>hs_code</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>scope_note</t>
         </is>
@@ -2399,10 +3110,15 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>Current scope</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>72; 73 (listed CN codes)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Scope 1 + listed precursors. Largest CBAM sector by EU import value (c.66% of CBAM imports).</t>
         </is>
@@ -2421,10 +3137,15 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>Current scope</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>76 (listed CN codes)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Scope 1 + listed precursors. Second-largest sector (c.23%).</t>
         </is>
@@ -2443,10 +3164,15 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>Current scope</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>2523</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Scope 1 + Scope 2 (indirect emissions covered).</t>
         </is>
@@ -2465,10 +3191,15 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>Current scope</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
           <t>3102; 3105; 2808; 2814</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Scope 1 + Scope 2 (indirect emissions covered). 1% default-value markup.</t>
         </is>
@@ -2487,12 +3218,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>Current scope</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>2804.10</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Scope 1. Residual category - negligible EU import volumes to date.</t>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Scope 1. Residual category - negligible EU import volumes to date. Never subject to the 50-tonne de minimis.</t>
         </is>
       </c>
     </row>
@@ -2509,34 +3245,44 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>Current scope</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>2716</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Scope 1. Not covered by the UK CBAM; excluded from the Serbian import tax.</t>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Scope 1. Not covered by the UK CBAM; excluded from the Serbian import tax. Never subject to the 50-tonne de minimis.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>UK-CBAM</t>
+          <t>EU-CBAM</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Iron &amp; steel</t>
+          <t>Downstream metal-intensive goods</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>72; 73 (listed commodity codes)</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Direct emissions + upstream Scope 3 precursors.</t>
+          <t>c.180 CN codes in the December 2025 proposal - NOT YET ADOPTED; do not use for trade-flow work</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>PROPOSED from 1 Jan 2028: steel- and aluminium-intensive downstream goods (metal articles, fabricated metals, machinery, vehicles and components, metal furniture). Council general approach 12 June 2026; EP vote expected Sept 2026.</t>
         </is>
       </c>
     </row>
@@ -2548,15 +3294,20 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Iron &amp; steel</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>76 (listed commodity codes)</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>72; 73 (listed commodity codes)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Direct emissions + upstream Scope 3 precursors.</t>
         </is>
@@ -2570,15 +3321,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>76 (listed commodity codes)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Direct emissions + upstream Scope 3 precursors.</t>
         </is>
@@ -2592,15 +3348,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Fertilizers</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>3102; 3105; 2808; 2814</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Direct emissions + upstream Scope 3 precursors.</t>
         </is>
@@ -2614,15 +3375,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Fertilizers</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2804.10</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>3102; 3105; 2808; 2814</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Direct emissions + upstream Scope 3 precursors.</t>
         </is>
@@ -2631,44 +3397,54 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>AU-BCA</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Scope 1. Recommended for INITIAL coverage (cement and clinker). Clinker identified as the most exposed commodity.</t>
+          <t>2804.10</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Direct emissions + upstream Scope 3 precursors.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>AU-BCA</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Lime</t>
+          <t>Refined fuel products</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Scope 1. Possible future coverage; further analysis recommended.</t>
+          <t>27 (subset) - not defined</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Government to publish a CALL FOR EVIDENCE on the fuel sector and is considering whether to bring refined fuel products into scope in future. No commitment, no date.</t>
         </is>
       </c>
     </row>
@@ -2680,17 +3456,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ammonia &amp; derivatives</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Scope 1. Possible future coverage; further analysis recommended.</t>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Scope 1. The ONLY sector recommended for initial coverage (cement and clinker). Clinker identified as the most exposed commodity. Still a recommendation, not law.</t>
         </is>
       </c>
     </row>
@@ -2702,17 +3483,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Iron &amp; steel</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>72; 73</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Scope 1. Possible future coverage; partly covered by domestic carbon pricing.</t>
+          <t>2522</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Scope 1. Second-phase candidate only; subject to further assessment.</t>
         </is>
       </c>
     </row>
@@ -2724,17 +3510,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Ammonia &amp; derivatives</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Scope 1. Possible future coverage; complex production pathways flagged.</t>
+          <t>2814</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Scope 1. Second-phase candidate only; subject to further assessment.</t>
         </is>
       </c>
     </row>
@@ -2746,61 +3537,76 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Iron &amp; steel</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2804.10</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Scope 1. Possible future coverage; listed among second-phase candidates.</t>
+          <t>72; 73</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Scope 1. Second-phase candidate only; partly covered by domestic carbon pricing already.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>RS-CIPIT</t>
+          <t>AU-BCA</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Glass</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Embedded emissions net of a reference emission value; EUR 4/tCO2e.</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Scope 1. Second-phase candidate only; complex production pathways flagged.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>RS-CIPIT</t>
+          <t>AU-BCA</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Fertilizers</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>3102; 3105</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Embedded emissions net of a reference emission value; EUR 4/tCO2e.</t>
+          <t>2804.10</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Scope 1. Second-phase candidate only; subject to further assessment.</t>
         </is>
       </c>
     </row>
@@ -2812,15 +3618,20 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Iron &amp; steel</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>72; 73</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Embedded emissions net of a reference emission value; EUR 4/tCO2e.</t>
         </is>
@@ -2834,15 +3645,20 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Fertilizers</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>3102; 3105</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Embedded emissions net of a reference emission value; EUR 4/tCO2e.</t>
         </is>
@@ -2851,44 +3667,54 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>NO-CBAM</t>
+          <t>RS-CIPIT</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Iron &amp; steel</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Intended alignment with EU CBAM; Norwegian regulation not yet adopted.</t>
+          <t>72; 73</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Embedded emissions net of a reference emission value; EUR 4/tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>NO-CBAM</t>
+          <t>RS-CIPIT</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Intended alignment with EU CBAM; Norwegian regulation not yet adopted.</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Embedded emissions net of a reference emission value; EUR 4/tCO2e.</t>
         </is>
       </c>
     </row>
@@ -2900,15 +3726,20 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Fertilizers</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>3102; 3105</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Intended alignment with EU CBAM; Norwegian regulation not yet adopted.</t>
         </is>
@@ -2922,15 +3753,20 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Iron &amp; steel</t>
+          <t>Electricity</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>72; 73</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>2716</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Intended alignment with EU CBAM; Norwegian regulation not yet adopted.</t>
         </is>
@@ -2944,15 +3780,20 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Fertilizers</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>3102; 3105</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Intended alignment with EU CBAM; Norwegian regulation not yet adopted.</t>
         </is>
@@ -2966,15 +3807,20 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Iron &amp; steel</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2804.10</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>72; 73</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Intended alignment with EU CBAM; Norwegian regulation not yet adopted.</t>
         </is>
@@ -2983,7 +3829,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>US-FPFA</t>
+          <t>NO-CBAM</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -2993,34 +3839,44 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
+          <t>Current scope</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>One of eight categories named in S. 1325; fee benchmarked to US pollution intensity. Bill not enacted.</t>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Intended alignment with EU CBAM; Norwegian regulation not yet adopted.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>US-FPFA</t>
+          <t>NO-CBAM</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>One of eight categories named in S. 1325. Bill not enacted.</t>
+          <t>2804.10</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Intended alignment with EU CBAM; Norwegian regulation not yet adopted.</t>
         </is>
       </c>
     </row>
@@ -3032,17 +3888,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Iron &amp; steel</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>72; 73</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>One of eight categories named in S. 1325. Bill not enacted.</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>One of eight categories named in S. 1325; fee benchmarked to US pollution intensity. Bill not enacted.</t>
         </is>
       </c>
     </row>
@@ -3054,15 +3915,20 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Fertilizers</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>3102; 3105; 2808; 2814</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>One of eight categories named in S. 1325. Bill not enacted.</t>
         </is>
@@ -3076,17 +3942,22 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Iron &amp; steel</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>One of eight categories named in S. 1325. Not covered by the EU or UK CBAMs.</t>
+          <t>72; 73</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>One of eight categories named in S. 1325. Bill not enacted.</t>
         </is>
       </c>
     </row>
@@ -3098,15 +3969,20 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Fertilizers</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>2804.10</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>3102; 3105; 2808; 2814</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>One of eight categories named in S. 1325. Bill not enacted.</t>
         </is>
@@ -3120,17 +3996,22 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Solar products</t>
+          <t>Glass</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>8541.43</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>One of eight categories named in S. 1325. Unique to the US proposal - no other BCA covers solar.</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>One of eight categories named in S. 1325. Not covered by the EU or UK CBAMs.</t>
         </is>
       </c>
     </row>
@@ -3142,61 +4023,76 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Batteries (long-duration storage)</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>One of eight categories named in S. 1325. Unique to the US proposal - no other BCA covers batteries.</t>
+          <t>2804.10</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>One of eight categories named in S. 1325. Bill not enacted.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>US-CCA</t>
+          <t>US-FPFA</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Iron &amp; steel</t>
+          <t>Solar products</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>72; 73</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
+          <t>8541.43</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>One of eight categories named in S. 1325. Unique to the US proposal - no other BCA covers solar. HS heading indicative.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>US-CCA</t>
+          <t>US-FPFA</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Aluminium</t>
+          <t>Batteries (long-duration storage)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
+          <t>8507</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>One of eight categories named in S. 1325. Unique to the US proposal - no other BCA covers batteries. HS heading indicative.</t>
         </is>
       </c>
     </row>
@@ -3208,15 +4104,20 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Iron &amp; steel</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>72; 73</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
         </is>
@@ -3230,15 +4131,20 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chemicals (certain)</t>
+          <t>Aluminium</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>28; 29 (subset)</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
         </is>
@@ -3247,7 +4153,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>TW-TRIAL</t>
+          <t>US-CCA</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -3257,40 +4163,104 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
+          <t>Current scope</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
           <t>2523</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Trial declaration only - no charge.</t>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Carbon intensity above a sectoral benchmark; bill not enacted.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Chemicals (certain)</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Current scope</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>28; 29 (subset)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Carbon intensity above a sectoral benchmark; bill not enacted. Sponsor materials also reference fossil fuels; statutory list not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t>TW-TRIAL</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Current scope</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Within the trial declaration scope. Reporting only - no charge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>TW-TRIAL</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Iron &amp; steel</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Current scope</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>72; 73</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>Trial declaration only - no charge.</t>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Within the trial declaration scope. Reporting only - no charge.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3302,7 +4272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3655,22 +4625,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>European Parliament plenary vote expected on scope expansion and the Temporary Decarbonisation Fund</t>
+          <t>Commission publishes guidance on CBAM verification and accreditation</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>To be followed by a Council vote and then negotiations on the final text; agreement targeted before end-2026.</t>
+          <t>Published 24 August 2026 for verifiers and National Accreditation Bodies, plus a procedure for verifier access to the CBAM Registry from 1 Sept 2026. First verifier accreditations expected around Sept 2026.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>https://www.consilium.europa.eu/en/press/press-releases/2026/06/12/council-moves-to-strengthen-the-eu-s-carbon-border-adjustment-mechanism/</t>
+          <t>https://taxation-customs.ec.europa.eu/news/european-commission-publishes-guidance-cbam-verifiers-and-accreditation-bodies-2026-08-24_en</t>
         </is>
       </c>
     </row>
@@ -3682,22 +4652,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Third quarterly CBAM certificate price published</t>
+          <t>Member state vote expected on the Art. 9 third-country carbon price implementing act</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Published 5 October 2026.</t>
+          <t>Draft published 13 May 2026, feedback closed 10 June 2026. Still not adopted, while importers are already incurring quarterly obligations. Would apply retroactively from 1 Jan 2026.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>https://taxation-customs.ec.europa.eu/carbon-border-adjustment-mechanism/price-cbam-certificates_en</t>
+          <t>https://taxation-customs.ec.europa.eu/news/carbon-price-paid-third-countries-2026-05-13_en</t>
         </is>
       </c>
     </row>
@@ -3709,22 +4679,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Weekly certificate pricing begins; 2027 default-value markup rises to 20%</t>
+          <t>European Parliament plenary vote expected on scope expansion and the Temporary Decarbonisation Fund</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Fourth quarterly price published 4 January 2027, weekly thereafter. Fertilizers excepted from the markup increase.</t>
+          <t>To be followed by a Council vote and then negotiations on the final text; agreement targeted before end-2026.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>https://taxation-customs.ec.europa.eu/carbon-border-adjustment-mechanism/price-cbam-certificates_en</t>
+          <t>https://www.consilium.europa.eu/en/press/press-releases/2026/06/12/council-moves-to-strengthen-the-eu-s-carbon-border-adjustment-mechanism/</t>
         </is>
       </c>
     </row>
@@ -3736,22 +4706,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>First CBAM certificates available for purchase by declarants</t>
+          <t>Third quarterly CBAM certificate price published</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>1 February 2027.</t>
+          <t>Published 5 October 2026.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>https://taxation-customs.ec.europa.eu/carbon-border-adjustment-mechanism_en</t>
+          <t>https://taxation-customs.ec.europa.eu/carbon-border-adjustment-mechanism/price-cbam-certificates_en</t>
         </is>
       </c>
     </row>
@@ -3763,22 +4733,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>First quarterly deadline for declarants to hold the required level of certificates</t>
+          <t>Weekly certificate pricing begins; 2027 default-value markup rises to 20%</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>31 March 2027.</t>
+          <t>Fourth quarterly price published 4 January 2027, weekly thereafter. Fertilizers excepted from the markup increase.</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>https://taxation-customs.ec.europa.eu/carbon-border-adjustment-mechanism_en</t>
+          <t>https://taxation-customs.ec.europa.eu/carbon-border-adjustment-mechanism/price-cbam-certificates_en</t>
         </is>
       </c>
     </row>
@@ -3790,17 +4760,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2027-09</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>First annual CBAM declaration and payment due, for 2026 imports</t>
+          <t>First CBAM certificates available for purchase by declarants</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>30 September 2027. The first real cash-flow event under any BCA.</t>
+          <t>1 February 2027.</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -3817,17 +4787,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2027-12</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Commission reports due on carbon leakage (including exports) and on default values and sector markups</t>
+          <t>First quarterly deadline for declarants to hold the required level of certificates</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Feeds the 2028 review of scope and methodology.</t>
+          <t>31 March 2027.</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -3844,17 +4814,17 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2028-01</t>
+          <t>2027-09</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Potential expansion to downstream products; default-value markup rises to 30%</t>
+          <t>First annual CBAM declaration and payment due, for 2026 imports</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Subject to conclusion of the ordinary legislative procedure.</t>
+          <t>30 September 2027. The first real cash-flow event under any BCA.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -3866,54 +4836,54 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>UK-CBAM</t>
+          <t>EU-CBAM</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2027-12</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>UK and EU agree to work toward linking their emissions trading systems</t>
+          <t>Commission reports due on carbon leakage (including exports) and on default values and sector markups</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Linkage could exempt or relieve bilateral trade from both CBAMs.</t>
+          <t>Feeds the 2028 review of scope and methodology.</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/news/eu-and-uk-commit-linking-emissions-trading-systems-landmark-cooperation-agreement</t>
+          <t>https://taxation-customs.ec.europa.eu/carbon-border-adjustment-mechanism_en</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>UK-CBAM</t>
+          <t>EU-CBAM</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2028-01</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>EU Climate Commissioner announces the start of formal EU-UK ETS linking negotiations</t>
+          <t>Potential expansion to downstream products; default-value markup rises to 30%</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>No completion timeline confirmed. Completing alignment before 1 Jan 2027 is widely seen as challenging.</t>
+          <t>Subject to conclusion of the ordinary legislative procedure.</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/news/eu-and-uk-commit-linking-emissions-trading-systems-landmark-cooperation-agreement</t>
+          <t>https://taxation-customs.ec.europa.eu/carbon-border-adjustment-mechanism_en</t>
         </is>
       </c>
     </row>
@@ -3925,22 +4895,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Primary CBAM legislation passed, confirming implementation from 1 January 2027</t>
+          <t>UK and EU agree to work toward linking their emissions trading systems</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Defines sectors and goods by commodity code, grants HMRC administration and enforcement powers, and provides the basis for secondary legislation.</t>
+          <t>Linkage could exempt or relieve bilateral trade from both CBAMs.</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/carbon-border-adjustment-mechanism-cbam-policy-summary</t>
+          <t>https://icapcarbonaction.com/en/news/eu-and-uk-commit-linking-emissions-trading-systems-landmark-cooperation-agreement</t>
         </is>
       </c>
     </row>
@@ -3952,22 +4922,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>First technical consultation on draft secondary legislation closes</t>
+          <t>EU Climate Commissioner announces the start of formal EU-UK ETS linking negotiations</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>24 March 2026. Administrative provisions, CBAM rate calculation, credit for origin carbon price, transitional provisions.</t>
+          <t>No completion timeline confirmed. Completing alignment before 1 Jan 2027 is widely seen as challenging.</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/carbon-border-adjustment-mechanism-cbam-policy-summary</t>
+          <t>https://icapcarbonaction.com/en/news/eu-and-uk-commit-linking-emissions-trading-systems-landmark-cooperation-agreement</t>
         </is>
       </c>
     </row>
@@ -3979,17 +4949,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Second technical consultation on draft secondary legislation closes</t>
+          <t>Primary CBAM legislation passed, confirming implementation from 1 January 2027</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>21 May 2026. Embedded-emissions methodology, monitoring requirements, verification standards.</t>
+          <t>Defines sectors and goods by commodity code, grants HMRC administration and enforcement powers, and provides the basis for secondary legislation.</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -4006,17 +4976,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>UK CBAM enters into force</t>
+          <t>First technical consultation on draft secondary legislation closes</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Default values and business guidance still to be published as at September 2026.</t>
+          <t>24 March 2026. Administrative provisions, CBAM rate calculation, credit for origin carbon price, transitional provisions.</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -4028,34 +4998,34 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>AU-BCA</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Final Carbon Leakage Review report released, recommending a BCA</t>
+          <t>Second technical consultation on draft secondary legislation closes</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Released 13 February 2026. Recommends a staged BCA for high-leakage-risk commodities starting with cement and clinker; rules out export rebates; recommends removing TEBA for covered commodities.</t>
+          <t>21 May 2026. Embedded-emissions methodology, monitoring requirements, verification standards.</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>https://www.dcceew.gov.au/climate-change/publications/carbon-leakage-review</t>
+          <t>https://www.gov.uk/government/publications/carbon-border-adjustment-mechanism-cbam-policy-summary</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>AU-BCA</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -4065,159 +5035,159 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Recommendations enter the 2026-27 Safeguard Mechanism review</t>
+          <t>Core secondary legislation made: SI 2026/802, 809 and 830</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Government response pending; no commitment to implement.</t>
+          <t>Made 13-14 July 2026, laid before the Commons 14 July, in force 1 Jan 2027. SI 2026/809 fixes how HMRC derives the CBAM rate from UK ETS prices and how importers claim carbon price relief. Emissions and verification regulations remain draft.</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>https://www.dcceew.gov.au/climate-change/emissions-reduction/review-carbon-leakage</t>
+          <t>https://www.legislation.gov.uk/uksi/2026/809/made</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>RS-CIPIT</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>National Assembly adopts the Law on Greenhouse Gas Emissions Tax and the Law on the Tax on Imports of Carbon-Intensive Products</t>
+          <t>HMRC publishes the first list of Qualifying Carbon Pricing Schemes</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Domestic and border carbon pricing introduced as a pair, both at EUR 4 per tonne CO2e. Several implementing bylaws still outstanding.</t>
+          <t>Published 27 August 2026, assessed as at 19 June 2026. Sixteen schemes recognised. The first published list of qualifying foreign carbon prices by any BCA; expressly non-exhaustive and kept under review.</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>https://www.pravno-informacioni-sistem.rs/</t>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>RS-CIPIT</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Carbon-intensive product import tax enters into force</t>
+          <t>HMRC registration expected to open via the Government Gateway</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Same day as the EU CBAM definitive phase. Covers iron &amp; steel, cement, fertilizers and aluminium; electricity and hydrogen are outside the import tax. First annual return due 31 May 2027.</t>
+          <t>Expected in the final quarter of 2026. Annual accounting period for 2027, moving to quarterly accounting from 2028.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>https://www.pravno-informacioni-sistem.rs/</t>
+          <t>https://www.gov.uk/government/collections/carbon-border-adjustment-mechanism</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>NO-CBAM</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Norway announces plans to implement a CBAM parallel to the EU's by 2027</t>
+          <t>UK CBAM enters into force</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Design intended to mirror the EU mechanism.</t>
+          <t>Default values and business guidance still to be published as at September 2026.</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
+          <t>https://www.gov.uk/government/publications/carbon-border-adjustment-mechanism-cbam-policy-summary</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>NO-CBAM</t>
+          <t>AU-BCA</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Target entry into force, pending incorporation of the EU CBAM Regulation into the EEA Agreement</t>
+          <t>Final Carbon Leakage Review report released, recommending a BCA</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Not yet incorporated as at September 2026.</t>
+          <t>Released 13 February 2026. Recommends a staged BCA for high-leakage-risk commodities starting with cement and clinker; rules out export rebates; recommends removing TEBA for covered commodities.</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
+          <t>https://www.dcceew.gov.au/climate-change/publications/carbon-leakage-review</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>US-FPFA</t>
+          <t>AU-BCA</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Foreign Pollution Fee Act of 2025 (S. 1325) introduced by Senators Cassidy and Graham</t>
+          <t>Recommendations enter the 2026-27 Safeguard Mechanism review</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Introduced 8 April 2025 and referred to the Senate Committee on Finance. Updates the 2023 bill (S. 3198, 118th Congress) after a public comment period. Not enacted as at September 2026.</t>
+          <t>Government response pending; no commitment to implement.</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325</t>
+          <t>https://www.dcceew.gov.au/climate-change/emissions-reduction/review-carbon-leakage</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>US-CCA</t>
+          <t>RS-CIPIT</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -4227,339 +5197,474 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Clean Competition Act of 2025 (S. 3523) introduced; referred to the Senate Committee on Finance</t>
+          <t>National Assembly adopts the Law on Greenhouse Gas Emissions Tax and the Law on the Tax on Imports of Carbon-Intensive Products</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Introduced 17 December 2025 by Senator Whitehouse with five co-sponsors; companion bill H.R. 6787 introduced in the House by Representative DelBene. Earliest stage of the legislative process.</t>
+          <t>Domestic and border carbon pricing introduced as a pair, both at EUR 4 per tonne CO2e. Several implementing bylaws still outstanding.</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523</t>
+          <t>https://www.pravno-informacioni-sistem.rs/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>TH-CBAM</t>
+          <t>RS-CIPIT</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Excise tax on petroleum products restructured to reflect carbon content at THB 200/tCO2e</t>
+          <t>Carbon-intensive product import tax enters into force</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>First step in a phased domestic carbon-pricing rollout, ahead of the Climate Change Act.</t>
+          <t>Same day as the EU CBAM definitive phase. Covers iron &amp; steel, cement, fertilizers and aluminium; electricity and hydrogen are outside the import tax. First annual return due 31 May 2027.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/ets/thailand</t>
+          <t>https://www.pravno-informacioni-sistem.rs/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>TH-CBAM</t>
+          <t>NO-CBAM</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Cabinet approves the Draft Climate Change Act</t>
+          <t>Norway announces plans to implement a CBAM parallel to the EU's by 2027</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2 December 2025. Establishes four carbon-pricing instruments including a CBAM on imported products modelled on the EU's.</t>
+          <t>Design intended to mirror the EU mechanism.</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/ets/thailand</t>
+          <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>TH-CBAM</t>
+          <t>NO-CBAM</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Third public hearing on the Draft Act completed</t>
+          <t>Target entry into force, pending incorporation of the EU CBAM Regulation into the EEA Agreement</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>8 April 2026. Bill progressing through the legislative process via the Office of the Council of State.</t>
+          <t>Not yet incorporated as at September 2026.</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/ets/thailand</t>
+          <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>TH-CBAM</t>
+          <t>US-FPFA</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Enforcement of the Climate Change Act anticipated</t>
+          <t>Foreign Pollution Fee Act of 2025 (S. 1325) introduced by Senators Cassidy and Graham</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Indicative; the CBAM itself requires subsequent ministerial regulation.</t>
+          <t>Introduced 8 April 2025 and referred to the Senate Committee on Finance. Updates the 2023 bill (S. 3198, 118th Congress) after a public comment period. Not enacted as at September 2026.</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/ets/thailand</t>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>TR-CLIM</t>
+          <t>US-CCA</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Climate Law No. 7552 published in the Official Gazette and enters into force</t>
+          <t>Clean Competition Act of 2025 (S. 3523) introduced; referred to the Senate Committee on Finance</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>9 July 2025, Official Gazette No. 32951. Legal basis for a national ETS and an enabling provision for a future CBAM.</t>
+          <t>Introduced 17 December 2025 by Senator Whitehouse with five co-sponsors; companion bill H.R. 6787 introduced in the House by Representative DelBene. Earliest stage of the legislative process.</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>TR-CLIM</t>
+          <t>TH-CBAM</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Turkish ETS pilot phase launches</t>
+          <t>Excise tax on petroleum products restructured to reflect carbon content at THB 200/tCO2e</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Secondary legislation being finalised; Carbon Market Board constituted.</t>
+          <t>First step in a phased domestic carbon-pricing rollout, ahead of the Climate Change Act.</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
+          <t>https://icapcarbonaction.com/en/ets/thailand</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>TW-TRIAL</t>
+          <t>TH-CBAM</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>2023-02</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Climate Change Response Act 2023 provides for carbon-related fees on imported goods</t>
+          <t>Cabinet approves the Draft Climate Change Act</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>The legal basis for any future border measure.</t>
+          <t>2 December 2025. Establishes four carbon-pricing instruments including a CBAM on imported products modelled on the EU's.</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+          <t>https://icapcarbonaction.com/en/ets/thailand</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>TW-TRIAL</t>
+          <t>TH-CBAM</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Carbon fee implementing regulations envisage a 'carbon leakage risk adjustment mechanism'</t>
+          <t>Third public hearing on the Draft Act completed</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Lower carbon rates for at-risk industries; does not appear to have been implemented.</t>
+          <t>8 April 2026. Bill progressing through the legislative process via the Office of the Council of State.</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+          <t>https://icapcarbonaction.com/en/ets/thailand</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>TW-TRIAL</t>
+          <t>TH-CBAM</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Ministry of Environment proposes a carbon border adjustment mechanism beginning with a trial declaration system</t>
+          <t>Enforcement of the Climate Change Act anticipated</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Cement and steel imports.</t>
+          <t>Indicative; the CBAM itself requires subsequent ministerial regulation.</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+          <t>https://icapcarbonaction.com/en/ets/thailand</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>TW-TRIAL</t>
+          <t>TR-CLIM</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Trial carbon-declaration system for cement and steel imports expected to launch</t>
+          <t>Climate Law No. 7552 published in the Official Gazette and enters into force</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Contingent on finalisation of the underlying legal framework.</t>
+          <t>9 July 2025, Official Gazette No. 32951. Legal basis for a national ETS and an enabling provision for a future CBAM.</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+          <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>CA-CONSULT</t>
+          <t>TR-CLIM</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>2021-08</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Department of Finance opens a consultation on border carbon adjustments for Canada</t>
+          <t>Turkish ETS pilot phase launches</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>No government response to consultation input has been published.</t>
+          <t>Secondary legislation being finalised; Carbon Market Board constituted.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>https://www.canada.ca/en/department-finance/programs/consultations/2021/border-carbon-adjustments/exploring-border-carbon-adjustments-canada.html</t>
+          <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>TW-TRIAL</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Climate Change Response Act 2023 provides for carbon-related fees on imported goods</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>The legal basis for any future border measure.</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>TW-TRIAL</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Carbon fee implementing regulations envisage a 'carbon leakage risk adjustment mechanism'</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Lower carbon rates for at-risk industries; does not appear to have been implemented.</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>TW-TRIAL</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Environment proposes a carbon border adjustment mechanism beginning with a trial declaration system</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Cement and steel imports.</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>TW-TRIAL</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Trial carbon-declaration system for cement and steel imports expected to launch</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Contingent on finalisation of the underlying legal framework.</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
           <t>CA-CONSULT</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Department of Finance opens a consultation on border carbon adjustments for Canada</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>No government response to consultation input has been published.</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.canada.ca/en/department-finance/programs/consultations/2021/border-carbon-adjustments/exploring-border-carbon-adjustments-canada.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CA-CONSULT</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Canada's industrial carbon price significantly weakened</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Reduces the carbon-leakage pressure that would motivate a Canadian BCA.</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>https://climateinstitute.ca/news/mou-with-alberta-puts-canadas-commitment-to-net-zero-emissions-by-2050-firmly-out-of-reach/</t>
         </is>
@@ -4579,7 +5684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4824,17 +5929,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Council general approach on strengthening the CBAM (12 June 2026)</t>
+          <t>CBAM verification - accredited verifiers and accreditation bodies</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Council position</t>
+          <t>Official page</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://www.consilium.europa.eu/en/press/press-releases/2026/06/12/council-moves-to-strengthen-the-eu-s-carbon-border-adjustment-mechanism/</t>
+          <t>https://taxation-customs.ec.europa.eu/carbon-border-adjustment-mechanism/cbam-verification_en</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -4846,22 +5951,22 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>UK-CBAM</t>
+          <t>EU-CBAM</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Carbon Border Adjustment Mechanism (CBAM): policy summary</t>
+          <t>Guidance for CBAM verifiers and National Accreditation Bodies (24 Aug 2026)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Policy paper</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/carbon-border-adjustment-mechanism-cbam-policy-summary</t>
+          <t>https://taxation-customs.ec.europa.eu/news/european-commission-publishes-guidance-cbam-verifiers-and-accreditation-bodies-2026-08-24_en</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -4873,22 +5978,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>UK-CBAM</t>
+          <t>EU-CBAM</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Factsheet: Carbon Border Adjustment Mechanism</t>
+          <t>Implementing Reg (EU) 2025/486 - authorised CBAM declarant status and appeals</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Factsheet</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/publications/factsheet-carbon-border-adjustment-mechanism-cbam/factsheet-carbon-border-adjustment-mechanism</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX%3A32025R0486</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -4900,22 +6005,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>UK-CBAM</t>
+          <t>EU-CBAM</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>House of Commons Library briefing CBP-9935: Carbon border adjustment mechanism</t>
+          <t>Carbon price paid in third countries - draft implementing act (13 May 2026)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Parliamentary briefing</t>
+          <t>Draft act</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://researchbriefings.files.parliament.uk/documents/CBP-9935/CBP-9935.pdf</t>
+          <t>https://taxation-customs.ec.europa.eu/news/carbon-price-paid-third-countries-2026-05-13_en</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -4927,22 +6032,22 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>AU-BCA</t>
+          <t>EU-CBAM</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Australia's Carbon Leakage Review report (final report)</t>
+          <t>Council general approach on strengthening the CBAM (12 June 2026)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Review report</t>
+          <t>Council position</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://www.dcceew.gov.au/climate-change/publications/carbon-leakage-review</t>
+          <t>https://www.consilium.europa.eu/en/press/press-releases/2026/06/12/council-moves-to-strengthen-the-eu-s-carbon-border-adjustment-mechanism/</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -4954,22 +6059,22 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>AU-BCA</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Carbon Leakage Review - review landing page</t>
+          <t>Carbon Border Adjustment Mechanism (CBAM): policy summary</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Official page</t>
+          <t>Policy paper</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://www.dcceew.gov.au/climate-change/emissions-reduction/review-carbon-leakage</t>
+          <t>https://www.gov.uk/government/publications/carbon-border-adjustment-mechanism-cbam-policy-summary</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -4981,22 +6086,22 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>RS-CIPIT</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Official Gazette of the Republic of Serbia (legal information system)</t>
+          <t>Factsheet: Carbon Border Adjustment Mechanism</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Legislation</t>
+          <t>Factsheet</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://www.pravno-informacioni-sistem.rs/</t>
+          <t>https://www.gov.uk/government/publications/factsheet-carbon-border-adjustment-mechanism-cbam/factsheet-carbon-border-adjustment-mechanism</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -5008,76 +6113,76 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>RS-CIPIT</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Green taxes in Serbia - what do you need to know? (rate, thresholds, default values)</t>
+          <t>List of current qualifying carbon pricing schemes (16 schemes)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Tax alert (secondary)</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://kpmg.com/rs/en/insights/tax-alerts/2025/12/green-taxes-in-serbia-what-do-you-need-to-know.html</t>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>RS-CIPIT</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Serbia rolls out taxes on GHG emissions and imported carbon-intensive products</t>
+          <t>SI 2026/809 - CBAM (Calculation of CBAM Rate and Determination of Carbon Price Relief) Regulations 2026</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>News (secondary)</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://balkangreenenergynews.com/serbia-rolls-out-taxes-on-greenhouse-gas-emissions-imported-carbon-intensive-products/</t>
+          <t>https://www.legislation.gov.uk/uksi/2026/809/made</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>NO-CBAM</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Miljodirektoratet - CBAM page</t>
+          <t>Work out your carbon price relief</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Regulatory page</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
+          <t>https://www.gov.uk/guidance/work-out-your-carbon-price-relief</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -5089,130 +6194,130 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>US-FPFA</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>S. 1325 - Foreign Pollution Fee Act of 2025 (bill record)</t>
+          <t>CBAM collection (registration, returns, record-keeping)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Official collection</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325</t>
+          <t>https://www.gov.uk/government/collections/carbon-border-adjustment-mechanism</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>US-FPFA</t>
+          <t>UK-CBAM</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>S. 1325 - full bill text as introduced</t>
+          <t>House of Commons Library briefing CBP-9935: Carbon border adjustment mechanism</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Bill text</t>
+          <t>Parliamentary briefing</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325/text</t>
+          <t>https://researchbriefings.files.parliament.uk/documents/CBP-9935/CBP-9935.pdf</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>US-FPFA</t>
+          <t>AU-BCA</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Foreign Pollution Fee Act - earlier discussion draft</t>
+          <t>Australia's Carbon Leakage Review report (final report)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Bill (draft)</t>
+          <t>Review report</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://www.cassidy.senate.gov/wp-content/uploads/2024/12/FPF-Discussion-Draft.pdf</t>
+          <t>https://www.dcceew.gov.au/climate-change/publications/carbon-leakage-review</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>US-CCA</t>
+          <t>AU-BCA</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>S. 3523 - Clean Competition Act (bill record)</t>
+          <t>Carbon Leakage Review - review landing page</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Official page</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523</t>
+          <t>https://www.dcceew.gov.au/climate-change/emissions-reduction/review-carbon-leakage</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>US-CCA</t>
+          <t>RS-CIPIT</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>S. 3523 - full bill text as introduced</t>
+          <t>Official Gazette of the Republic of Serbia (legal information system)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Bill text</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523/text</t>
+          <t>https://www.pravno-informacioni-sistem.rs/</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -5224,22 +6329,22 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>US-CCA</t>
+          <t>RS-CIPIT</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>H.R. 6787 - Clean Competition Act (House companion)</t>
+          <t>Green taxes in Serbia - what do you need to know? (rate, thresholds, default values)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Tax alert (secondary)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>https://www.congress.gov/bill/119th-congress/house-bill/6787/text</t>
+          <t>https://kpmg.com/rs/en/insights/tax-alerts/2025/12/green-taxes-in-serbia-what-do-you-need-to-know.html</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -5251,76 +6356,76 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>TH-CBAM</t>
+          <t>RS-CIPIT</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ICAP - Thailand country profile (Draft Climate Change Act)</t>
+          <t>Serbia rolls out taxes on GHG emissions and imported carbon-intensive products</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Official-adjacent profile</t>
+          <t>News (secondary)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/ets/thailand</t>
+          <t>https://balkangreenenergynews.com/serbia-rolls-out-taxes-on-greenhouse-gas-emissions-imported-carbon-intensive-products/</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>TR-CLIM</t>
+          <t>NO-CBAM</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Turkiye adopts landmark climate law, paving the way for a national ETS</t>
+          <t>Miljodirektoratet - CBAM page</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>News / legal summary</t>
+          <t>Regulatory page</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
+          <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>TW-TRIAL</t>
+          <t>US-FPFA</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Ministry of Environment - carbon border adjustment mechanism trial declaration proposal</t>
+          <t>S. 1325 - Foreign Pollution Fee Act of 2025 (bill record)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Announcement</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -5332,25 +6437,241 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>US-FPFA</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>S. 1325 - full bill text as introduced</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Bill text</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325/text</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>US-FPFA</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Foreign Pollution Fee Act - earlier discussion draft</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Bill (draft)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cassidy.senate.gov/wp-content/uploads/2024/12/FPF-Discussion-Draft.pdf</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>S. 3523 - Clean Competition Act (bill record)</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>S. 3523 - full bill text as introduced</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Bill text</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523/text</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>H.R. 6787 - Clean Competition Act (House companion)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>https://www.congress.gov/bill/119th-congress/house-bill/6787/text</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TH-CBAM</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>ICAP - Thailand country profile (Draft Climate Change Act)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Official-adjacent profile</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/ets/thailand</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>TR-CLIM</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Turkiye adopts landmark climate law, paving the way for a national ETS</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>News / legal summary</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>TW-TRIAL</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Ministry of Environment - carbon border adjustment mechanism trial declaration proposal</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Announcement</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
           <t>CA-CONSULT</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Exploring border carbon adjustments for Canada</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Consultation</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/department-finance/programs/consultations/2021/border-carbon-adjustments/exploring-border-carbon-adjustments-canada.html</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -5365,6 +6686,907 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="92" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>REFERENCE - Which foreign carbon pricing schemes each instrument recognises for relief against its own charge. One row per INSTRUMENT x SCHEME. As at September 2026 ONLY THE UK has published an actual list (16 schemes, 27 Aug 2026); every other instrument has either a methodology without a list, a different mechanism entirely, or nothing yet. The UK list is expressly NON-EXHAUSTIVE - an unlisted scheme may still qualify. Emissions covered by free allowances never qualify, because no effective carbon price was paid on them.</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>instrument_id</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>scheme_name</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>scheme_jurisdiction</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>recognition_status</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>source_url</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Australia Safeguard Mechanism</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Baseline-and-credit scheme for large industrial facilities. Australia is itself weighing a BCA (see AU-BCA).</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Canada Federal Output-Based Pricing System (OBPS)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Federal industrial carbon price. Note Canada's industrial carbon price was significantly weakened in May 2026 - monitor whether it continues to qualify.</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Chile Carbon Tax</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Carbon tax on large stationary sources.</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>China National Emissions Trading System</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Expanded in March 2025 to steel, cement and aluminium - the CBAM-targeted sectors. China is the largest single source of EU CBAM-covered imports.</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>EU Emissions Trading System (EU ETS)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>European Union</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Relief is reduced to the extent emissions were covered by free allowances. UK-EU ETS linkage under negotiation would change this treatment.</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Indian Carbon Credit Trading Scheme (CCTS)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Recognised by the UK. India remains among the most vocal WTO critics of the EU CBAM; the EU-India FTA contains a dedicated CBAM annex.</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Japan GX-ETS</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Phased GX framework.</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Kazakhstan Emissions Trading System (KAZ ETS)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Operating since 2013; covers power, extractives and heavy industry. Free allocation is extensive, so the effective price actually paid may be low.</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Korea Emissions Trading System (K-ETS)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Republic of Korea</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Operating since 2015; fourth phase reforms from 2026.</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Montenegro Emissions Trading Scheme</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>One of two Western Balkans schemes; contrast Serbia, whose carbon tax is listed separately.</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>New Zealand Emissions Trading Scheme (NZ ETS)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>One of the longest-running ETSs. New Zealand co-sponsored the WTO submission on measurement methodologies (WT/CTE/W/269/Rev.5).</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Serbia Carbon Tax</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>The domestic GHG Emissions Tax, not the import tax (RS-CIPIT). EUR 4/tCO2e.</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Singapore Carbon Tax</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Raised from 2024 and applies to large emitters. Singapore has been active in Paris Art. 6 cooperation.</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>South Africa Carbon Tax</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Extensive allowances mean the effective price may be low; relief depends on the effective price actually paid.</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Swiss Emissions Trading System (CHETS)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Linked to the EU ETS. Switzerland examined and declined its own CBAM in 2023.</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>UK-CBAM</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Taiwan Carbon Fee</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Chinese Taipei</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Recognised - on the published list</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Chinese Taipei is itself developing a trial carbon declaration system (see TW-TRIAL).</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>EU-CBAM</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>(no list published)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>No list published - draft methodology only</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Art. 9 permits deduction of a carbon price effectively paid at origin, but the implementing act is still a draft (13 May 2026). Four recognition pathways; Paris Art. 6.2/6.4 credits capped at 10%; free allowances, rebates and indirect cost compensation reduce the price counted as effectively paid. Member state vote expected Sept 2026. Commission may later publish default carbon prices per country.</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>https://taxation-customs.ec.europa.eu/news/carbon-price-paid-third-countries-2026-05-13_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>RS-CIPIT</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>(no list published)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>No list published - evidence-based credit</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Liability reduced where an emissions charge was already paid at origin, on submission of evidence. No qualifying schemes are named and the assessing methodology sits in outstanding bylaws.</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pravno-informacioni-sistem.rs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>AU-BCA</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>(none - measure not adopted)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Recommended approach only</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Explicit carbon prices only, credited against the difference between the origin price and the Australian benchmark. No list can exist until the measure is adopted.</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dcceew.gov.au/climate-change/publications/carbon-leakage-review</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>NO-CBAM</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>(follows the EU)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>European Union</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Intended EU alignment</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Would apply the EU Art. 9 regime once the CBAM Regulation is incorporated into the EEA Agreement. Depends on an EU act that is itself still draft.</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>US-FPFA</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>(partner country agreements)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Different mechanism - not carbon-price recognition</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>No carbon-price deduction. The fee is instead reduced for goods from a 'partner country' under an international partnership agreement under ss. 201-202. No such agreement exists. A 2x multiplier applies to non-market economies.</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>US-CCA</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>(not applicable)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable by design</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>No origin carbon-price deduction: the charge falls equally on domestic producers and importers, so equalisation is achieved domestically rather than by crediting foreign prices.</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>TH-CBAM</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>(to be determined)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>To be determined</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>To be set by ministerial regulation under the draft Climate Change Act.</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/ets/thailand</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>TR-CLIM</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>(to be determined)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>To be determined</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>No CBAM designed, so no recognition regime exists.</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TW-TRIAL</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>(to be determined)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>To be determined</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Trial declaration only; no charge and therefore no relief mechanism yet.</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>CA-CONSULT</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>(not applicable)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Not applicable - dormant</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>No design was produced.</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>https://www.canada.ca/en/department-finance/programs/consultations/2021/border-carbon-adjustments/exploring-border-carbon-adjustments-canada.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5595,7 +7817,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5711,13 +7933,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5924,32 +8146,66 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Solar products</t>
+          <t>Downstream metal-intensive goods</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>8541.43</t>
+          <t>c.180 CN codes (proposed)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>US Foreign Pollution Fee Act only. No other BCA covers solar; HS heading indicative, verify against the bill's schedule.</t>
+          <t>EU CBAM PROSPECTIVE only - the December 2025 proposal for expansion from 2028. Not adopted; codes not final.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Refined fuel products</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>27 (subset)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>UK CBAM PROSPECTIVE only - subject to a promised call for evidence. No commitment, no date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Solar products</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>8541.43</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>US Foreign Pollution Fee Act only. No other BCA covers solar; HS heading indicative, verify against the bill's schedule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>Batteries (long-duration storage)</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>8507</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>US Foreign Pollution Fee Act only. No other BCA covers batteries; HS heading indicative, verify against the bill's schedule.</t>
         </is>
@@ -5958,193 +8214,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="76" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="46" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>REFERENCE - Taxonomy for the Scope 1 / 2 / 3 columns in the Instruments tab, requested in the pilot dataset. IMPORTANT: these labels are a COMPARABILITY OVERLAY, not the legal test. Each instrument defines 'embedded' or 'embodied' emissions in its own methodology annex. Read this tab before relying on a scope cell in advice.</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>scope_term</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>how BCAs currently treat it</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>authority</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Scope 1</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Direct greenhouse gas emissions from sources owned or controlled by the producing installation - e.g. fuel combustion in a kiln or blast furnace, and process emissions such as calcination in cement production.</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Covered by every BCA in this tracker. It is the common denominator across the EU, UK, Serbian, Australian and Californian measures.</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>GHG Protocol Corporate Standard; Reg (EU) 2023/956 Annex IV</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Scope 2</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Indirect emissions from generation of purchased electricity, steam, heating or cooling consumed by the installation.</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>EU CBAM: cement and fertilizers only. UK CBAM: deferred to 2029 at the earliest. Australia: not recommended. This is the single largest design divergence between the EU and UK mechanisms.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>GHG Protocol Corporate Standard; Reg (EU) 2023/956 Annex IV</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Scope 3 (upstream, precursors only)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Emissions embedded in specified input goods (precursors) that are themselves within the mechanism's product scope - not full value-chain Scope 3.</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>EU CBAM: listed precursors only. UK CBAM: systematically includes upstream precursor emissions, which is why UK coverage is described as broader on Scope 3 than the EU's.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Reg (EU) 2023/956 Annex IV; HMRC/HM Treasury CBAM policy summary (2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Scope 3 (full value chain)</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>All other indirect emissions across the upstream and downstream value chain, including transport, distribution and use of sold products.</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>NOT covered by any BCA currently in force or in draft. Occasionally raised in modelling studies (e.g. semiconductor exposure analyses) but not in any legal instrument.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>GHG Protocol Corporate Value Chain (Scope 3) Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Embedded / embodied emissions</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>The operative legal term in most BCA instruments. Defined by each instrument's own methodology rather than by the GHG Protocol scopes, and usually equates to Scope 1 plus a defined subset of Scope 2 and precursor Scope 3.</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Use the instrument's own definition when advising. The tracker maps each instrument onto the Scope 1/2/3 vocabulary for comparability, but the legal test is the instrument's own methodology annex.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Reg (EU) 2023/956 Art. 3 and Annex IV; UK CBAM draft secondary legislation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Direct emissions (UK usage)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>The UK CBAM's term for emissions in scope: direct emissions embodied in imported goods, including those embodied in CBAM-covered precursor goods.</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Note the terminological trap: the UK's 'direct emissions' expressly INCLUDES upstream precursor (Scope 3) emissions, so it is not equivalent to Scope 1.</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>HM Revenue &amp; Customs / HM Treasury - CBAM policy summary (2026)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6156,300 +8225,94 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
-    <col width="68" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="84" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="84" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REFERENCE - Jurisdictions checked during the September 2026 sweep that do NOT (yet) have a BCA instrument, and so have no row in the Instruments tab. Recorded so the negative finding is auditable and so nobody re-researches them. Promote a row to the Instruments tab only when a primary source shows an actual proposal or instrument.</t>
+          <t>REFERENCE - Controlled vocabulary for the 'coverage' column in the Sectors tab. Only two values are permitted. This is the distinction between what an instrument covers TODAY and what it might cover LATER, and it is a separate question from whether the instrument is in force. Getting these two axes confused is the single easiest way to misread the tracker.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>jurisdiction</t>
+          <t>coverage_value</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>position</t>
+          <t>meaning</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>what exists now</t>
+          <t>shown in the dashboard as</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>why it is on the watchlist</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>source_url</t>
+          <t>warning</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Current scope</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Considered and declined</t>
+          <t>The sector sits within the instrument's own defined scope, as set out in the legislation, bill or official recommendation.</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Government decided against introducing a CBAM parallel to the EU's, in a report published June 2023. Swiss-origin goods are exempt from the EU CBAM because the Swiss and EU emissions trading systems are linked.</t>
+          <t>Tick in the coverage matrix.</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Monitor only. A reversal would most likely follow from changes to the EU-Switzerland ETS link.</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>https://icapcarbonaction.com/en/news/swiss-ets-reform-comes-force</t>
+          <t>IMPORTANT: this says nothing about whether the instrument itself is law. Australia's cement entry is 'Current scope' but the whole instrument is only a recommendation - always read this column together with the instrument's status.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Prospective</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Domestic pricing in development</t>
+          <t>The sector has been officially flagged for possible future addition - a second phase, a proposed expansion, or a promised call for evidence - but is NOT within scope today.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Draft ETS law released for public consultation 15 May 2026. Compliance obligation would rise from 10% in 2028 to 100% in 2034, explicitly mirroring the EU CBAM phase-in. No Ukrainian BCA proposed.</t>
+          <t>Hollow circle in the coverage matrix.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>High relevance: Ukraine is among the most EU CBAM-exposed economies (8.1% of global exports). Parliament has been asked to seek a CBAM exemption.</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>https://icapcarbonaction.com/en/news/ukraine-releases-draft-ets-law-consultations</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Republic of Korea</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Domestic pricing only</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>K-ETS operating since 2015 and covering c.73-79% of national emissions. Fourth phase reforms from 2026. No Korean BCA proposed.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Watch as the most advanced candidate for an EU CBAM Art. 9 origin carbon-price deduction. No jurisdiction had received formal Commission confirmation as at April 2026.</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>https://icapcarbonaction.com/en/ets/korea-emissions-trading-scheme</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Domestic pricing only</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>GX framework and phased carbon pricing. No BCA proposed. Active at the WTO on interoperability and non-binding measurement guidance.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Identified in academic work as a likely future adopter if the EU CBAM broadens. Co-sponsor of WT/CTE/W/269/Rev.5 on measurement methodologies.</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>https://icapcarbonaction.com/en/ets/japan-tokyo-cap-and-trade-program</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Domestic pricing only</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>SBCE (Sistema Brasileiro de Comercio de Emissoes) established by federal law in December 2024; rules still being finalised. No Brazilian BCA proposed.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Watch for Art. 9 deduction eligibility. Hosted COP 30 and launched the Integrated Forum on Climate Change and Trade.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>https://icapcarbonaction.com/en/ets/brazil</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Domestic pricing only; opposed to BCAs</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Carbon Credit Trading Scheme (CCTS) under the Bureau of Energy Efficiency. No Indian BCA proposed. India has been among the most vocal WTO critics of the EU CBAM.</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Highest-priority watch item: the EU-India FTA (concluded Jan 2026) contains the first dedicated CBAM annex (Annex 14-A), a likely template for future agreements.</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>https://beeindia.gov.in/</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Domestic pricing only</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>National ETS expanded in March 2025 to cover steel, cement and aluminium - the CBAM-targeted sectors. No Chinese BCA proposed.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Largest single source of EU CBAM-covered imports (16.9% in 2024). Has tabled a WTO submission on carbon-standards fragmentation (G/TBT/W/818).</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>https://icapcarbonaction.com/en/ets/china-national-ets</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Conceptual - external advice only</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Ministry of Investment, Trade and Industry has been advised to consider a Malaysian CBAM with a pilot in the steel sector. No government proposal identified.</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Low confidence: the source is external advice, not a government position. Do not promote to the Instruments tab without a primary source.</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>https://zerocarbon-analytics.org/finance/carbon-border-adjustment-mechanisms-require-coordinated-global-action/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Russian Federation</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Opposed; WTO dispute</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>No BCA. Filed a WTO request for consultations against the EU in May 2025 concerning the CBAM and aspects of the EU ETS. No further procedural steps taken at the time of the IISD 2026 report.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Watch the dispute docket - the first WTO challenge to a BCA.</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.iisd.org/publications/report/state-of-border-carbon-adjustments-2026</t>
+          <t>Never treat a prospective row as coverage. HS codes on prospective rows are indicative at best and must not be used for trade-flow calculations.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BCA_tracker_only_BCA.xlsx
+++ b/BCA_tracker_only_BCA.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sectors" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carbon_price_linkage" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carbon_price_recognition" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Status_legend" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category_legend" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector_legend" sheetId="8" state="visible" r:id="rId8"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>YES - HMRC published a list of 16 Qualifying Carbon Pricing Schemes on 27 Aug 2026 (assessed as at 19 June 2026), the first such list published by any BCA. Criteria are in SI 2026/809. The list is expressly NON-EXHAUSTIVE: unlisted schemes may still qualify, regional schemes are under review, and HMRC invites submissions. Emissions covered by FREE ALLOWANCES do not qualify, because no effective carbon price was paid; rebates and refunds reduce relief; in some cases no relief is available at all. The liable person, not HMRC, is responsible for determining eligibility. See the Carbon_price_linkage tab for the full list.</t>
+          <t>YES - HMRC published a list of 16 Qualifying Carbon Pricing Schemes on 27 Aug 2026 (assessed as at 19 June 2026), the first such list published by any BCA. Criteria are in SI 2026/809. The list is expressly NON-EXHAUSTIVE: unlisted schemes may still qualify, regional schemes are under review, and HMRC invites submissions. Emissions covered by FREE ALLOWANCES do not qualify, because no effective carbon price was paid; rebates and refunds reduce relief; in some cases no relief is available at all. The liable person, not HMRC, is responsible for determining eligibility. See the Carbon_price_recognition tab for the full list.</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
@@ -2870,12 +2870,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Third-country carbon price linkage</t>
+          <t>Third-country carbon price recognition</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>The Carbon_price_linkage tab records which foreign carbon pricing schemes each instrument recognises. As at Sept 2026 only the UK has published a list (16 schemes, 27 Aug 2026). The EU's Art. 9 implementing act remains a draft, so no EU list exists and importers in the definitive phase are already incurring obligations without settled deduction rules. Treat the UK list as the only authoritative recognition list currently in existence, and note it is expressly non-exhaustive.</t>
+          <t>The Carbon_price_recognition tab records which foreign carbon pricing schemes each instrument recognises. As at Sept 2026 only the UK has published a list (16 schemes, 27 Aug 2026). The EU's Art. 9 implementing act remains a draft, so no EU list exists and importers in the definitive phase are already incurring obligations without settled deduction rules. Treat the UK list as the only authoritative recognition list currently in existence, and note it is expressly non-exhaustive.</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6700,12 +6700,13 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="92" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>REFERENCE - Which foreign carbon pricing schemes each instrument recognises for relief against its own charge. One row per INSTRUMENT x SCHEME. As at September 2026 ONLY THE UK has published an actual list (16 schemes, 27 Aug 2026); every other instrument has either a methodology without a list, a different mechanism entirely, or nothing yet. The UK list is expressly NON-EXHAUSTIVE - an unlisted scheme may still qualify. Emissions covered by free allowances never qualify, because no effective carbon price was paid on them.</t>
+          <t>REFERENCE - Which foreign carbon pricing schemes each instrument RECOGNISES for relief against its own charge. Deliberately called 'recognition', not 'linkage': linkage is a different legal concept (mutual recognition of allowances between two trading systems, as with the EU-Swiss ETS or the proposed EU-UK link). One row per INSTRUMENT x SCHEME. As at September 2026 ONLY THE UK has published an actual list (16 schemes, 27 Aug 2026); every other instrument has a methodology without a list, a different mechanism entirely, or nothing yet. The UK list is expressly NON-EXHAUSTIVE. Emissions covered by free allowances never qualify, because no effective carbon price was paid on them. scheme_url: 8 entries link to the scheme's own official page; the other 8 route to the World Bank Carbon Pricing Dashboard factsheets because no official page was verified - replace those as you confirm them.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6713,6 +6714,7 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -6745,6 +6747,11 @@
           <t>source_url</t>
         </is>
       </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>scheme_url</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -6777,6 +6784,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dcceew.gov.au/climate-change/emissions-reduction/safeguard-mechanism</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -6809,6 +6821,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>https://carbonpricingdashboard.worldbank.org/explore-factsheets</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -6841,6 +6858,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>https://carbonpricingdashboard.worldbank.org/explore-factsheets</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -6873,6 +6895,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/ets/china-national-ets</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -6905,6 +6932,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>https://climate.ec.europa.eu/areas-action/carbon-markets/eu-emissions-trading-system-eu-ets_en</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -6937,6 +6969,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>https://carbonpricingdashboard.worldbank.org/explore-factsheets</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6969,6 +7006,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>https://carbonpricingdashboard.worldbank.org/explore-factsheets</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -7001,6 +7043,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>https://carbonpricingdashboard.worldbank.org/explore-factsheets</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -7033,6 +7080,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/ets/korea-emissions-trading-scheme</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -7065,6 +7117,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>https://carbonpricingdashboard.worldbank.org/explore-factsheets</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -7097,6 +7154,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>https://carbonpricingdashboard.worldbank.org/explore-factsheets</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -7129,6 +7191,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.pravno-informacioni-sistem.rs/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -7161,6 +7228,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nccs.gov.sg/singapores-climate-action/mitigation-efforts/carbontax/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -7193,6 +7265,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sars.gov.za/customs-and-excise/excise/environmental-levy-products/carbon-tax/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -7225,6 +7302,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>https://icapcarbonaction.com/en/news/swiss-ets-reform-comes-force</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -7257,6 +7339,11 @@
           <t>https://www.gov.uk/government/publications/uk-cbam-current-qualifying-carbon-pricing-schemes/carbon-border-adjustment-mechanism-list-of-current-qualifying-carbon-pricing-schemes</t>
         </is>
       </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>https://carbonpricingdashboard.worldbank.org/explore-factsheets</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -7289,6 +7376,11 @@
           <t>https://taxation-customs.ec.europa.eu/news/carbon-price-paid-third-countries-2026-05-13_en</t>
         </is>
       </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -7321,6 +7413,11 @@
           <t>https://www.pravno-informacioni-sistem.rs/</t>
         </is>
       </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -7353,6 +7450,11 @@
           <t>https://www.dcceew.gov.au/climate-change/publications/carbon-leakage-review</t>
         </is>
       </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -7385,6 +7487,11 @@
           <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
         </is>
       </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -7417,6 +7524,11 @@
           <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325</t>
         </is>
       </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -7449,6 +7561,11 @@
           <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523</t>
         </is>
       </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -7481,6 +7598,11 @@
           <t>https://icapcarbonaction.com/en/ets/thailand</t>
         </is>
       </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -7513,6 +7635,11 @@
           <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
         </is>
       </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -7545,6 +7672,11 @@
           <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
         </is>
       </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -7577,10 +7709,15 @@
           <t>https://www.canada.ca/en/department-finance/programs/consultations/2021/border-carbon-adjustments/exploring-border-carbon-adjustments-canada.html</t>
         </is>
       </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BCA_tracker_only_BCA.xlsx
+++ b/BCA_tracker_only_BCA.xlsx
@@ -22,8 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage_legend" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope_legend" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multilateral" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -487,18 +486,21 @@
     <col width="44" customWidth="1" min="11" max="11"/>
     <col width="56" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="62" customWidth="1" min="14" max="14"/>
     <col width="58" customWidth="1" min="15" max="15"/>
-    <col width="46" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="62" customWidth="1" min="18" max="18"/>
-    <col width="58" customWidth="1" min="19" max="19"/>
-    <col width="58" customWidth="1" min="20" max="20"/>
-    <col width="44" customWidth="1" min="21" max="21"/>
-    <col width="44" customWidth="1" min="22" max="22"/>
-    <col width="52" customWidth="1" min="23" max="23"/>
-    <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="60" customWidth="1" min="25" max="25"/>
+    <col width="48" customWidth="1" min="16" max="16"/>
+    <col width="58" customWidth="1" min="17" max="17"/>
+    <col width="46" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="56" customWidth="1" min="20" max="20"/>
+    <col width="62" customWidth="1" min="21" max="21"/>
+    <col width="58" customWidth="1" min="22" max="22"/>
+    <col width="58" customWidth="1" min="23" max="23"/>
+    <col width="44" customWidth="1" min="24" max="24"/>
+    <col width="44" customWidth="1" min="25" max="25"/>
+    <col width="52" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="60" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
@@ -531,6 +533,9 @@
       <c r="W1" s="2" t="n"/>
       <c r="X1" s="2" t="n"/>
       <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -600,60 +605,75 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
+          <t>legal_basis</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>source_status</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
           <t>Third Country Adjustment</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>Qualifying Carbon Prices</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>Default Values</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>De Minimis Threshold</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>Calculation in brief</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>Verification</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>Review and Appeal</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>Revenue Use</t>
         </is>
       </c>
-      <c r="V2" s="3" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>primary_source</t>
         </is>
       </c>
-      <c r="W2" s="3" t="inlineStr">
+      <c r="Z2" s="3" t="inlineStr">
         <is>
           <t>official_url</t>
         </is>
       </c>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
+      <c r="AB2" s="3" t="inlineStr">
         <is>
           <t>One Line Summary of the Measure</t>
         </is>
@@ -727,60 +747,75 @@
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
-          <t>YES - deduction for the carbon price effectively paid in the country of origin; explicit carbon prices only (Art. 9). Draft implementing act published May 2026 sets the deduction methodology and would allow limited use of Paris Agreement Art. 6.4 offsets.</t>
+          <t>Regulation (EU) 2023/956, as amended by Reg (EU) 2025/2083. Implementing Regs (EU) 2025/2546 (verification), 2025/2547 (embedded emissions), 2025/2548 (certificate price), 2025/2620 (free-allocation adjustment), 2025/2621 (default values), 2025/486 (declarant status); Delegated Reg (EU) 2025/2551 (accreditation).</t>
         </is>
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
+          <t>Official primary sources only (EUR-Lex, European Commission). Two EU import-share figures in the Sectors tab are IISD analysis and are attributed there.</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>YES. Art. 9 lets an authorised declarant claim a reduction in the certificates to be surrendered, corresponding to the carbon price already effectively paid in the country of origin for the declared embedded emissions, so the same tonne is not priced twice. Explicit carbon prices only. Art. 9(4) empowers the Commission to set the detailed rules by implementing act - see Qualifying Carbon Prices for its status.</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
           <t>NO PUBLISHED LIST. Art. 9 allows deduction of a carbon price 'effectively paid' at origin, but the implementing act is still a DRAFT: published 13 May 2026, feedback closed 10 June 2026, member state vote expected September 2026. The draft sets four recognition pathways, caps Paris Art. 6.2/6.4 credits at 10% of the deduction, and creates a new 'independent person' certification role. Free allowances, baseline exemptions, tax rebates and indirect cost compensation all REDUCE the price counted as effectively paid. The Commission may publish default carbon prices per third country. The draft would apply retroactively from 1 Jan 2026. Contrast the UK, which has already published a list.</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>YES - country- and product-specific default values adopted by implementing/delegated acts (Nov-Dec 2025). Markup on default values: 10% (2026), 20% (2027), 30% (from 2028); fertilizers 1%.</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>50 tonnes of imported CBAM goods per importer per year (cumulative net mass). IMPORTANT: the threshold does NOT apply to hydrogen or electricity, which remain in scope at any volume. Introduced by Reg (EU) 2025/2083, replacing the earlier EUR 150-per-consignment exemption. Expected to exempt c.182,000 additional importers while still covering 99% of in-scope emissions.</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>Number of CBAM certificates = embedded emissions, reduced by the free-allocation adjustment factor and by the effective carbon price paid at origin. Certificate price in 2026 = the VOLUME-WEIGHTED AVERAGE of EU ETS auction clearing prices over the quarter, published in the first calendar week after each quarter ends, and applying only to goods imported in that quarter; from 2027 the Commission publishes a weekly price instead. Surrender obligation phases in with the EU ETS free-allowance phase-out (the CBAM factor is 2.5% of embedded emissions in 2026, rising to 100% in 2034). Published prices are held in the Prices tab, not here.</t>
-        </is>
-      </c>
       <c r="S3" s="4" t="inlineStr">
         <is>
-          <t>Actual emissions must be verified by a verifier accredited by an EU/EEA National Accreditation Body under Reg (EC) 765/2008. Accreditation conditions: Delegated Reg (EU) 2025/2551. Verification rules: Implementing Reg (EU) 2025/2546 - risk-based, REASONABLE ASSURANCE standard, with site visits; the report records a satisfactory or unsatisfactory opinion. Verifiers must register in the CBAM Registry within two months of accreditation but not before 1 Sept 2026, and issue verification reports in the Registry from Jan 2027. First accreditations expected around Sept 2026; Commission guidance for verifiers and NABs published 24 Aug 2026. Reports may be reviewed by the Commission and by National Competent Authorities. NABs are peer-evaluated by European co-operation for Accreditation.</t>
+          <t>50 tonnes of CBAM goods per importer per calendar year (cumulative net mass), introduced by Reg (EU) 2025/2083 in place of the earlier EUR 150-per-consignment exemption. IMPORTANT: the threshold does not cover hydrogen or electricity, which remain in scope at any volume. The European Commission estimated the change would take roughly 182,000 further importers out of scope while still capturing about 99% of covered emissions (European Commission, CBAM simplification proposal, 2025).</t>
         </is>
       </c>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>Administered by MEMBER STATE National Competent Authorities, not the Commission. Refusal or revocation of authorised CBAM declarant status carries a right of appeal under national law, and the NCA must register the existence and outcome of the appeal in the CBAM Registry (Implementing Reg (EU) 2025/486). An appeal does NOT suspend a revocation decision. Substantive challenges run through member state administrative and judicial review, with a possible preliminary reference to the CJEU under TFEU Art. 267 - so the practical remedy varies by member state of import.</t>
+          <t>One CBAM certificate per tonne of CO2e embedded in the goods you import. Three things cut the bill: the free-allocation adjustment (Art. 31), any carbon price already paid at origin (Art. 9), and the phase-in factor - only 2.5% of embedded emissions need cover in 2026, rising to 100% by 2034. The certificate price tracks the EU ETS: a quarterly average in 2026, weekly from 2027. From 2027 you must hold certificates for at least 50% of emissions to date at each quarter end.</t>
         </is>
       </c>
       <c r="U3" s="4" t="inlineStr">
         <is>
+          <t>STEP 1 - embedded emissions, calculated under the methods in Annex IV (Art. 7); for Annex II goods only direct emissions count. STEP 2 - deduct free allocation: the certificates to surrender are adjusted to reflect the free EU ETS allowances given to equivalent EU installations under Art. 10a of Directive 2003/87/EC (Art. 31; method in Implementing Reg (EU) 2025/2620). STEP 3 - deduct any carbon price effectively paid at origin (Art. 9). STEP 4 - apply the price. For each quarter of 2026 the Commission calculates the certificate price as the quarterly average of the AUCTION CLEARING PRICES of EU ETS allowances - the price successful bidders actually pay - determined under Art. 7 of Delegated Reg (EU) 2023/2830. It is calculated in the first calendar week after the quarter ends and published the following working day. From 1 January 2027 the same average is calculated weekly instead. (Implementing Reg (EU) 2025/2548, Arts. 1-3, adopted under Art. 21(3) of the CBAM Regulation.) STEP 5 - hold and surrender. At each quarter end a declarant must hold certificates covering at least 50% of cumulative embedded emissions since the start of the calendar year (Art. 22(2), as amended by Reg (EU) 2025/2083). Surrender falls due by 30 September of the following year; certificates held in excess may be repurchased (Art. 23). Published prices are recorded in the Prices tab, not here.</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>WHO VERIFIES: an independent verifier accredited by a national accreditation body under Reg (EC) 765/2008 (Arts. 8 and 18; accreditation conditions in Delegated Reg (EU) 2025/2551). TO WHAT STANDARD: risk-based verification to a REASONABLE ASSURANCE level, with site visits, under Implementing Reg (EU) 2025/2546 and Annex VI. The report records a satisfactory or unsatisfactory opinion, so the existence of a report proves nothing on its own - read the opinion and any unresolved findings. TIMING: verifiers register in the CBAM Registry within two months of accreditation and not before 1 September 2026, and issue reports in the Registry from January 2027. OVERSIGHT: the Commission or the competent authority may review a declaration under Art. 19(2). Commission guidance for verifiers and accreditation bodies was published on 24 August 2026.</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>WHO DECIDES: the national competent authority of the member state of import, not the Commission. AGAINST A STATUS DECISION: refusal or revocation of authorised CBAM declarant status carries a right of appeal under national law. The authority must record the appeal and its outcome in the CBAM Registry, and an appeal does NOT suspend a revocation (Implementing Reg (EU) 2025/486). AGAINST AN ASSESSMENT: the Commission or the competent authority may review a CBAM declaration under Art. 19(2); a challenge then runs through that member state's administrative and judicial review, with a possible preliminary reference to the CJEU under TFEU Art. 267. PRACTICAL POINT: the remedy, the time limits and the forum all depend on the member state of import - establish that first.</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
           <t>General budget of the EU and of EU member states. A separate legislative proposal would create a 2-year Temporary Decarbonisation Fund allocating 25% of CBAM revenues in 2028-2029 to EU energy-intensive industry.</t>
         </is>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>European Commission - Regulation (EU) 2023/956 as amended by Regulation (EU) 2025/2083</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>https://taxation-customs.ec.europa.eu/carbon-border-adjustment-mechanism_en</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr">
         <is>
           <t>World's first ETS-based BCA in force. Q2 2026 certificate price EUR 75.28/tCO2e. First declaration and payment fall due 30 September 2027 for 2026 imports.</t>
         </is>
@@ -854,60 +889,75 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
+          <t>UK primary CBAM legislation passed March 2026; SI 2026/802 (administration), SI 2026/809 (CBAM rate and carbon price relief), SI 2026/830 (transitory provisions), all made 13-14 July 2026 and in force 1 Jan 2027. Emissions and Verification Regulations still in draft.</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Official primary sources only (legislation.gov.uk, HMRC/HM Treasury guidance).</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
           <t>YES - liability reduced where the embodied emissions are subject to a deductible carbon price overseas; explicit carbon prices only. Mechanism for claiming the credit is set out in draft secondary legislation.</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>YES - HMRC published a list of 16 Qualifying Carbon Pricing Schemes on 27 Aug 2026 (assessed as at 19 June 2026), the first such list published by any BCA. Criteria are in SI 2026/809. The list is expressly NON-EXHAUSTIVE: unlisted schemes may still qualify, regional schemes are under review, and HMRC invites submissions. Emissions covered by FREE ALLOWANCES do not qualify, because no effective carbon price was paid; rebates and refunds reduce relief; in some cases no relief is available at all. The liable person, not HMRC, is responsible for determining eligibility. See the Carbon_price_recognition tab for the full list.</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>YES - reporting on default values permitted; from 2027 a single default value per product will apply. Values and methodology STILL UNPUBLISHED as at Sept 2026; the draft Emissions and Verification Regulations remain outstanding.</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>GBP 50,000 of imports by value over a rolling 12-month period.</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>Structured as a TAX collected by HMRC through direct-tax channels, not as tradable certificates. The rate is set separately for each CBAM sector, reflecting the UK ETS price adjusted for the free allocation granted to that sector and a sectoral reduction factor updated annually as free allowances are phased out; adjusted quarterly. Liability is reduced by any deductible overseas carbon price.</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>Emissions and Verification Regulations were still DRAFT as at Sept 2026, and default values remain unpublished. For carbon price relief, reg 9 of SI 2026/809 requires the importer to obtain a 'carbon pricing verification form' completed by a verifier and provided by that verifier to the installation that manufactured the good, in a form published by HMRC. Importers may use independently verified actual emissions or default values. Records supporting a relief claim must be kept for SIX YEARS from the day after the end of the accounting period covered by the return.</t>
-        </is>
-      </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
-          <t>HMRC administers UK CBAM as a TAX, so disputes follow ordinary UK tax procedure: HMRC statutory review, then appeal to the First-tier Tribunal (Tax Chamber) - not the customs or environmental enforcement routes that apply under the EU CBAM. This is the single clearest procedural divergence between the two mechanisms and matters for forum and timing. Existing HMRC penalty regimes apply, with specifics to be confirmed.</t>
+          <t>A tax, not a certificate market. HMRC sets a rate per tonne for each of the five sectors, derived from the UK ETS price and reduced to reflect the free allocation that sector still receives. Multiply your embedded emissions by that rate, then deduct any qualifying overseas carbon price already paid. You must register once imports pass GBP 50,000 in a rolling 12 months.</t>
         </is>
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
+          <t>A TAX collected by HMRC, not a tradable certificate. THE RATE: set separately for each of the five CBAM sectors, derived from the UK ETS price and then reduced by a sectoral factor reflecting the free allocation that sector still receives; updated annually and adjusted quarterly. The rate-setting mechanism is in the Carbon Border Adjustment Mechanism (Calculation of CBAM Rate and Determination of Carbon Price Relief) Regulations 2026, SI 2026/809. THE BASE: emissions embodied in the goods, using either independently verified actual data or default values. THE RELIEF: liability is reduced by the effective carbon price already paid under a qualifying overseas scheme (SI 2026/809, regs 6-13). ACCOUNTING PERIOD: annual for 2027, moving to quarterly from 2028. Specified scrap products in the aluminium and iron &amp; steel sectors are excluded by commodity code.</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>The Emissions and Verification Regulations were still in DRAFT as at September 2026, and default values remain unpublished. FOR CARBON PRICE RELIEF: reg 9 of SI 2026/809 requires the importer to obtain a 'carbon pricing verification form', completed by a verifier and provided by that verifier to the installation that manufactured the good, in a form published by HMRC. The importer must use the data in that form to compute the relief (reg 10). RECORDS: evidence supporting a relief claim must be kept for SIX YEARS from the day after the end of the accounting period covered by the return (reg 14).</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>UK CBAM is administered by HMRC as a TAX, so disputes follow ordinary UK tax procedure: HMRC statutory review, then appeal to the First-tier Tribunal (Tax Chamber). That is not the customs or environmental enforcement route used under the EU CBAM, and it is the clearest procedural divergence between the two mechanisms - it changes the forum, the time limits and the practical burden. HMRC's existing penalty regimes apply, with the specifics still to be confirmed.</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
           <t>General budget.</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>HM Revenue &amp; Customs and HM Treasury - CBAM policy summary (updated 16 July 2026); SI 2026/809 (rate calculation and carbon price relief), made 13 July 2026</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>https://www.gov.uk/government/publications/carbon-border-adjustment-mechanism-cbam-policy-summary</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>Operational rulebook largely complete: SI 2026/802, 809 and 830 were made 13-14 July 2026, in force 1 Jan 2027. Emissions and verification rules remain draft and default values unpublished. EU-UK ETS linkage under negotiation and could relieve bilateral trade from both CBAMs.</t>
         </is>
@@ -981,60 +1031,75 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
+          <t>None - the measure is a recommendation of the Carbon Leakage Review final report (released 13 February 2026). Any instrument would sit within the Safeguard Mechanism framework.</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>Official primary source only (DCCEEW review report).</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
           <t>YES (recommended) - explicit carbon prices only. Liability turns in part on the difference between the effective explicit carbon price in the country of origin and the Australian benchmark price.</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Recommended approach only: EXPLICIT carbon prices, credited by reference to the difference between the effective explicit carbon price in the country of origin and the Australian benchmark price. No list of qualifying schemes exists, and none can until the measure is adopted. Note that Australia's own Safeguard Mechanism appears on the UK's qualifying list.</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>RECOMMENDED - the review recommends 'suitable default emissions intensity values' aligned to emerging international standards while minimising administrative burden. No values published.</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>Not specified in the final report.</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>Not law - a recommendation. The proposal would charge an import only on the emissions ABOVE the Safeguard Mechanism baseline for that product, and only to the extent the origin country's explicit carbon price falls short of Australia's. A product at or below the baseline would pay nothing.</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>Liability calculated by reference to (a) emissions above the Safeguard Mechanism emissions-intensity baseline, and (b) the difference between the effective explicit carbon price in the country of origin and the Australian benchmark price. Because the Safeguard Mechanism charges only emissions above a baseline, imports at or below the baseline would face no liability.</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>Not designed. The review recommends default emissions intensity values aligned to emerging international standards in order to minimise administrative burden, which implies a lighter-touch model than the EU's accredited-verifier architecture, but no verification regime has been specified.</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>Not designed. The review did not address importer review or appeal rights. If a BCA were built onto the Safeguard Mechanism, the Clean Energy Regulator's existing NGER administrative framework would be the natural host, but nothing has been proposed - do not rely on any assumed route.</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>Recommended to be channelled to support implementation and industrial decarbonisation objectives in developing trade-partner countries.</t>
         </is>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Department of Climate Change, Energy, the Environment and Water - Carbon Leakage Review, final report (released 13 February 2026; review conducted July 2023 - March 2025)</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>https://www.dcceew.gov.au/climate-change/publications/carbon-leakage-review</t>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>A recommendation of an independent review, NOT government policy. Initial coverage cement and clinker; lime, hydrogen, ammonia and derivatives, iron &amp; steel and glass flagged as possible future additions. Clinker was identified as the most exposed commodity.</t>
         </is>
@@ -1108,62 +1173,77 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
+          <t>Law on the Tax on Imports of Carbon-Intensive Products, Official Gazette of the Republic of Serbia, adopted December 2025; companion Law on Greenhouse Gas Emissions Tax. Several implementing bylaws outstanding.</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>Official gazette is the governing text but is not readily deep-linkable; rate, thresholds and default-value provisions were confirmed against tax-practitioner summaries (KPMG; Balkan Green Energy News), which are recorded in Sources as Secondary. Verify against the gazette before advising.</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
           <t>YES - liability reduced where an emissions charge has already been paid in the country of origin, on submission of appropriate evidence.</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>No published list. Liability is reduced where an emissions charge has already been paid in the country of origin, on submission of appropriate evidence, but the law does not name qualifying schemes and the assessing methodology sits in outstanding bylaws. Note that Serbia's own carbon tax appears on the UK's qualifying list.</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>YES - default values are provided in the legislation. Importers may instead report independently verified actual emissions; verification must be carried out by bodies accredited under the International Accreditation Forum (IAF) system.</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>Importers of fewer than 5 tonnes of a covered product in a calendar year are not taxpayers. Note this is far tighter than the EU threshold (50 tonnes).</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>Tax base = actual or default embedded emissions of the imported product, reduced by prescribed reference emission values, taxed at EUR 4 per tonne CO2e (converted to dinars at the National Bank of Serbia middle rate on the last day of the tax period). Liability is reduced by any emissions charge already paid at origin. Annual return due 31 May for the preceding year. The EUR 4 rate is roughly 5% of the Q1 2026 EU CBAM certificate price of EUR 75.36.</t>
-        </is>
-      </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>A flat EUR 4 per tonne of embedded CO2e, less a prescribed reference emission value and less any carbon charge already paid at origin. Under 5 tonnes of a product in a year and you are not a taxpayer at all. One return a year, due 31 May.</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>Tax base = actual or default embedded emissions of the imported product, reduced by prescribed reference emission values, taxed at EUR 4 per tonne CO2e (converted to dinars at the National Bank of Serbia middle rate on the last day of the tax period). Liability is reduced by any emissions charge already paid at origin. Annual return due 31 May for the preceding year. For comparison, the EUR 4 rate is roughly 5% of the EU CBAM certificate price for the same period (see the Prices tab).</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
         <is>
           <t>Importers may report independently verified actual emissions or use the statutory default values. Verification must be carried out by bodies accredited under the INTERNATIONAL ACCREDITATION FORUM (IAF) system - a materially different anchor from the EU's National Accreditation Body route, and one that may admit a wider pool of verifiers.</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr">
         <is>
           <t>NOT SPECIFIED in either law as published. General Serbian tax-procedure rights - objection to the Tax Administration, then administrative court - would ordinarily apply, but the carbon legislation is silent and several implementing bylaws were outstanding at adoption. Read the Official Gazette text directly before advising a client on remedies.</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>Not specified in the law. The companion GHG Emissions Tax offers electricity producers a 20% tax credit for eligible decarbonisation investment, capped at 80% of liability.</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>Official Gazette of the Republic of Serbia - Law on the Tax on Imports of Carbon-Intensive Products (adopted by the National Assembly, December 2025)</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>https://www.pravno-informacioni-sistem.rs/</t>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>The second BCA in the world to enter into force, at EUR 4/tCO2e. Adopted as one of a pair with the domestic Law on Greenhouse Gas Emissions Tax; Serbia is among the most EU CBAM-exposed economies (7.1% of its global exports). Several implementing bylaws were still outstanding at adoption.</t>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>The second BCA in the world to enter into force, at EUR 4/tCO2e. Adopted as one of a pair with the domestic Law on Greenhouse Gas Emissions Tax. Serbia is among the most EU CBAM-exposed economies, at 7.1% of its global exports (IISD, State of Border Carbon Adjustments 2026). Several implementing bylaws were still outstanding at adoption.</t>
         </is>
       </c>
     </row>
@@ -1235,60 +1315,75 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
+          <t>None yet - commencement depends on incorporation of Reg (EU) 2023/956 into the EEA Agreement. No Norwegian implementing regulation adopted.</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>Official primary source only (Norwegian Environment Agency).</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
           <t>Intended to align with the EU CBAM (explicit carbon prices only). Not yet set out in Norwegian regulation.</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Intended to follow the EU's Art. 9 regime once the CBAM Regulation is incorporated into the EEA Agreement. Nothing adopted in Norwegian law, and the EU act on which it would depend is itself still a draft.</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>Intended to align with the EU CBAM. Not yet published.</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>Intended to align with the EU CBAM (50 tonnes per year). Not yet confirmed.</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>Intended to copy the EU calculation exactly. Nothing is adopted in Norwegian law yet, so there is no Norwegian method to apply.</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t>Intended to follow the EU CBAM methodology in full.</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="V7" s="4" t="inlineStr">
         <is>
           <t>Intended alignment with the EU model (accredited verifiers, reasonable assurance). No Norwegian implementing regulation adopted.</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>Not yet established. Would be expected to follow Norwegian administrative appeal procedure once regulations are adopted, but nothing is specified.</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>Not specified.</t>
         </is>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>Norwegian Environment Agency (Miljodirektoratet) - CBAM: justering av karbonpris for import av varer til EOS (2026)</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>https://www.miljodirektoratet.no/ansvarsomrader/internasjonalt/eu-regelverk/cbam/</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="AB7" s="4" t="inlineStr">
         <is>
           <t>Treat the 2027 date as a target, not a legal commencement date - the EEA incorporation step is the binding constraint. Norwegian goods are already exempt from the EU CBAM through the EU-EEA ETS relationship.</t>
         </is>
@@ -1362,60 +1457,75 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
+          <t>S. 1325, 119th Congress, introduced 8 April 2025; referred to the Senate Committee on Finance. Not enacted.</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>Official primary source only (congress.gov bill text as introduced).</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
           <t>NO carbon-price deduction of the EU/UK type - the benchmark is US pollution intensity, not a carbon price. BUT the fee is reduced for goods from a "partner country" under an international partnership agreement meeting the conditions in ss. 201-202 of the bill, which is the closest analogue and a materially different legal route.</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>NO carbon-price recognition mechanism. The bill instead reduces the fee for goods from a 'partner country' under an international partnership agreement satisfying ss. 201-202. No such agreement exists. A 2x multiplier applies to covered products from non-market economies, which cuts the opposite way.</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>A fee on imports whose pollution intensity exceeds the US average for the same product. Doubled for goods from non-market economies. Reduced for countries that conclude a partnership agreement with the US. No equivalent charge falls on US producers.</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>Fee determined by the amount by which the pollution intensity of the imported product exceeds the US baseline pollution intensity for that product, doubled for non-market economies, and reduced under any applicable partnership agreement.</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>Not specified in the bill as introduced. Pollution intensity is determined against US benchmarks, with GHGs measured as CO2e on a 100-year GWP basis per 40 CFR Part 98 subpart A table A-1. The bill does not establish an accreditation or third-party verification regime of the EU/UK type.</t>
         </is>
       </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>Not specified in the bill as introduced. The bill gives the Secretary of Commerce anti-evasion powers, including prohibiting imports from an evading country or producer, but sets out no importer-facing review or appeal route against an intensity determination.</t>
         </is>
       </c>
-      <c r="U8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>U.S. Senate - S. 1325, Foreign Pollution Fee Act of 2025 (Cassidy, Graham), introduced 8 April 2025</t>
         </is>
       </c>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>https://www.congress.gov/bill/119th-congress/senate-bill/1325</t>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="AB8" s="4" t="inlineStr">
         <is>
           <t>Introduced 8 April 2025, updating a 2023 bill after a public comment period. Not enacted. A border charge with no domestic carbon price raises different GATT Art. III:2 / Art. XX questions from the EU and UK models, and the non-market-economy multiplier raises MFN questions under Art. I:1.</t>
         </is>
@@ -1489,60 +1599,75 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
+          <t>S. 3523, 119th Congress, introduced 17 December 2025, with House companion H.R. 6787; referred to the Senate Committee on Finance. Not enacted.</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Official primary source only (congress.gov bill text as introduced).</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
           <t>N/A - not linked to an economy-wide domestic carbon price, so no origin carbon-price deduction of the EU/UK type. The bill instead equalises by charging domestic producers on the same basis.</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>N/A - there is no origin carbon-price deduction, because the charge falls equally on domestic producers and importers. Equalisation is achieved by charging domestic output on the same basis rather than by crediting foreign prices.</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>Not specified in the bill as introduced; baselines are derived from reported facility data rather than published default values.</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr">
         <is>
           <t>Not specified in the bill as introduced.</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>One charge applied identically to US producers and importers: the amount by which a product's carbon intensity exceeds its industry's 2025 baseline, multiplied by a starting price of USD 60 a tonne. The baseline tightens each year, so the same product pays more over time.</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
         <is>
           <t>Charge = (carbon intensity of the good less the applicable percentage of the baseline carbon intensity of its covered national industry) x relevant quantity x the cost of pollution. The cost of pollution is reported as starting at USD 60 per tonne. The applicable percentage tightens over time, so the effective baseline falls.</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr">
+      <c r="V9" s="4" t="inlineStr">
         <is>
           <t>For domestic producers the charge builds on facility-level emissions already reported to the EPA. For imports the bill relies on reported carbon intensity measured against the 2025 baseline for the covered national industry; no separate accreditation regime is established in the bill as introduced.</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr">
+      <c r="W9" s="4" t="inlineStr">
         <is>
           <t>Not specified in the bill as introduced. Because the measure would amend the Internal Revenue Code, ordinary US tax assessment, refund and Tax Court procedures would be the natural route, but the bill does not address this.</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr">
+      <c r="X9" s="4" t="inlineStr">
         <is>
           <t>Reinvested in decarbonisation: 75% to a Domestic Industrial Decarbonization Program administered by the Department of Energy, with the balance including international support for cleaner manufacturing in developing countries.</t>
         </is>
       </c>
-      <c r="V9" s="4" t="inlineStr">
+      <c r="Y9" s="4" t="inlineStr">
         <is>
           <t>U.S. Senate - S. 3523, Clean Competition Act (Whitehouse, with Blumenthal, Heinrich, Schatz, Welch, Van Hollen); House companion H.R. 6787 (DelBene), introduced 17 December 2025</t>
         </is>
       </c>
-      <c r="W9" s="4" t="inlineStr">
+      <c r="Z9" s="4" t="inlineStr">
         <is>
           <t>https://www.congress.gov/bill/119th-congress/senate-bill/3523</t>
         </is>
       </c>
-      <c r="X9" s="4" t="inlineStr">
+      <c r="AA9" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y9" s="4" t="inlineStr">
+      <c r="AB9" s="4" t="inlineStr">
         <is>
           <t>Introduced 17 December 2025 and referred to the Senate Committee on Finance; earliest stage of the legislative process. The fourth iteration of a bill first introduced in 2022 (S. 4355).</t>
         </is>
@@ -1616,60 +1741,75 @@
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
+          <t>Draft Climate Change Act, approved by Cabinet 2 December 2025; third public hearing completed 8 April 2026. Not enacted; the CBAM itself requires subsequent ministerial regulation.</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>No official English text located. Content drawn from ICAP's country profile, recorded in Sources as Secondary. Treat every parameter as provisional.</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
           <t>To be determined - not specified in the draft Act.</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
+      <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>To be determined by ministerial regulation. The draft Act provides the framework only.</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>To be determined - not specified in the draft Act.</t>
         </is>
       </c>
-      <c r="Q10" s="5" t="inlineStr">
+      <c r="S10" s="5" t="inlineStr">
         <is>
           <t>To be determined - not specified in the draft Act.</t>
         </is>
       </c>
-      <c r="R10" s="5" t="inlineStr">
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>Not yet decided. The draft Act creates the power to price emissions embedded in imports; the method, the covered goods and the rate all come later by ministerial regulation.</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
         <is>
           <t>To be determined by ministerial regulation. The draft Act provides the enabling framework only.</t>
         </is>
       </c>
-      <c r="S10" s="5" t="inlineStr">
+      <c r="V10" s="5" t="inlineStr">
         <is>
           <t>To be determined. The draft Act's ETS and carbon-tax components envisage MRV infrastructure administered by the Department of Climate Change and Environment, but no CBAM-specific verification or assurance standard is specified.</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr">
+      <c r="W10" s="5" t="inlineStr">
         <is>
           <t>To be determined by ministerial regulation. No importer review or appeal route appears in the draft Act.</t>
         </is>
       </c>
-      <c r="U10" s="5" t="inlineStr">
+      <c r="X10" s="5" t="inlineStr">
         <is>
           <t>Climate Fund - the draft Act establishes a Climate Fund financed in part by ETS and CBAM revenues, constituted as a juristic person and non-ministerial state agency.</t>
         </is>
       </c>
-      <c r="V10" s="5" t="inlineStr">
+      <c r="Y10" s="5" t="inlineStr">
         <is>
           <t>ICAP - Thailand; Draft Climate Change Act approved by Cabinet 2 December 2025</t>
         </is>
       </c>
-      <c r="W10" s="5" t="inlineStr">
+      <c r="Z10" s="5" t="inlineStr">
         <is>
           <t>https://icapcarbonaction.com/en/ets/thailand</t>
         </is>
       </c>
-      <c r="X10" s="5" t="inlineStr">
+      <c r="AA10" s="5" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y10" s="5" t="inlineStr">
+      <c r="AB10" s="5" t="inlineStr">
         <is>
           <t>ADDED 2026-09. The first Asian CBAM to reach draft-legislation stage. Cabinet-approved 2 Dec 2025; third public hearing completed 8 April 2026; before the Office of the Council of State and Parliament.</t>
         </is>
@@ -1743,62 +1883,77 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
+          <t>Climate Law No. 7552, Official Gazette No. 32951, 9 July 2025. No CBAM designed; the Ministry of Trade is empowered to determine scope by implementing legislation.</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>Law reference is official (Official Gazette). Descriptive detail drawn from ICAP, recorded in Sources as Secondary.</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
           <t>To be determined.</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>To be determined - no CBAM has been designed, so no recognition regime exists.</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>To be determined.</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>To be determined.</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to calculate - no Turkish CBAM has been designed. The Climate Law only creates the power to introduce one.</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>To be determined by implementing legislation. No mechanism has been designed as at September 2026.</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr">
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>To be determined. The Climate Law establishes a Carbon Market Board and an MRV framework for the national ETS; any CBAM verification architecture would follow from implementing legislation.</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="W11" s="4" t="inlineStr">
         <is>
           <t>To be determined. No CBAM assessment exists to dispute.</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr">
+      <c r="X11" s="4" t="inlineStr">
         <is>
           <t>Not specified.</t>
         </is>
       </c>
-      <c r="V11" s="4" t="inlineStr">
+      <c r="Y11" s="4" t="inlineStr">
         <is>
           <t>Climate Law No. 7552, Official Gazette of 9 July 2025 No. 32951; ICAP - Turkiye adopts landmark climate law (2025)</t>
         </is>
       </c>
-      <c r="W11" s="4" t="inlineStr">
+      <c r="Z11" s="4" t="inlineStr">
         <is>
           <t>https://icapcarbonaction.com/en/news/turkiye-adopts-landmark-climate-law-paving-way-national-ets</t>
         </is>
       </c>
-      <c r="X11" s="4" t="inlineStr">
+      <c r="AA11" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>ENABLING PROVISION ONLY - no Turkish CBAM has been designed. Turkiye is the second-largest source of EU CBAM-covered imports (11.4% in 2024) and among the most exposed EU trading partners.</t>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>ENABLING PROVISION ONLY - no Turkish CBAM has been designed; the provision is contingent on allowance auctioning and rising domestic carbon costs under the Turkish ETS. Turkiye was the second-largest source of EU CBAM-covered imports in 2024, at 11.4% (IISD, State of Border Carbon Adjustments 2026).</t>
         </is>
       </c>
     </row>
@@ -1870,60 +2025,75 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
+          <t>Climate Change Response Act 2023 (basis for carbon-related fees on imports); carbon fee implementing regulations 2024. No border charge in force.</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>Official primary source only (Ministry of Environment announcement).</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
           <t>To be determined.</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>To be determined. Note that Chinese Taipei's own carbon fee appears on the UK's qualifying list.</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>To be determined.</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>To be determined.</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to calculate. The trial asks importers of cement and steel to declare emissions; there is no charge attached.</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
         <is>
           <t>Trial reporting only at this stage; no charge. The underlying legal framework is still being finalised.</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr">
+      <c r="V12" s="4" t="inlineStr">
         <is>
           <t>Trial declaration only. Importers of cement and steel would report carbon emissions data; no charge, and no verification or assurance standard has been set.</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr">
+      <c r="W12" s="4" t="inlineStr">
         <is>
           <t>To be determined. There is no charge at the trial stage, so there is no assessment to dispute.</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr">
+      <c r="X12" s="4" t="inlineStr">
         <is>
           <t>Not specified.</t>
         </is>
       </c>
-      <c r="V12" s="4" t="inlineStr">
+      <c r="Y12" s="4" t="inlineStr">
         <is>
           <t>Ministry of Environment - proposal for a carbon border adjustment mechanism beginning with a trial declaration system (2025); Climate Change Response Act 2023</t>
         </is>
       </c>
-      <c r="W12" s="4" t="inlineStr">
+      <c r="Z12" s="4" t="inlineStr">
         <is>
           <t>https://enews.moenv.gov.tw/moenv-news/zh-tw/News/2363</t>
         </is>
       </c>
-      <c r="X12" s="4" t="inlineStr">
+      <c r="AA12" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y12" s="4" t="inlineStr">
+      <c r="AB12" s="4" t="inlineStr">
         <is>
           <t>Already present in the pilot dataset but previously near-empty; now populated. Legal basis in the Climate Change Response Act 2023. A declaration trial, not a charging mechanism.</t>
         </is>
@@ -1997,60 +2167,75 @@
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
+          <t>None - Department of Finance consultation, 2021. No instrument was proposed and no government response published.</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>Official primary source only (Department of Finance consultation paper).</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
           <t>N/A - no design was produced.</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>N/A - no design was produced. Note that Canada's Federal OBPS appears on the UK's qualifying list.</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>N/A - no design was produced.</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>N/A - no design was produced.</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>Nothing to calculate - the 2021 consultation never produced a design.</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
         <is>
           <t>N/A - no design was produced.</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>N/A - no design was produced.</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="W13" s="4" t="inlineStr">
         <is>
           <t>N/A - no design was produced.</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
+      <c r="X13" s="4" t="inlineStr">
         <is>
           <t>N/A - no design was produced.</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr">
+      <c r="Y13" s="4" t="inlineStr">
         <is>
           <t>Government of Canada, Department of Finance - Exploring border carbon adjustments for Canada (2021)</t>
         </is>
       </c>
-      <c r="W13" s="4" t="inlineStr">
+      <c r="Z13" s="4" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/department-finance/programs/consultations/2021/border-carbon-adjustments/exploring-border-carbon-adjustments-canada.html</t>
         </is>
       </c>
-      <c r="X13" s="4" t="inlineStr">
+      <c r="AA13" s="4" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y13" s="4" t="inlineStr">
+      <c r="AB13" s="4" t="inlineStr">
         <is>
           <t>Dormant. Canada's industrial carbon price was significantly weakened in May 2026, reducing the leakage pressure that would otherwise motivate a BCA. Category corrected from 'BCA' to 'Proposal'.</t>
         </is>
@@ -2058,7 +2243,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2491,7 +2676,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Includes iron and steel articles. The largest CBAM sector by EU import value (c.66% of CBAM-covered imports).</t>
+          <t>Includes iron and steel articles. Listed in Annex I to Reg (EU) 2023/956.</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2693,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Unwrought aluminium plus listed articles. Second-largest EU CBAM sector (c.23%).</t>
+          <t>Unwrought aluminium plus listed articles. Listed in Annex I to Reg (EU) 2023/956.</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3328,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>High relevance: Ukraine is among the most EU CBAM-exposed economies (8.1% of global exports). Parliament has been asked to seek a CBAM exemption.</t>
+          <t>Among the most EU CBAM-exposed economies, at 8.1% of global exports (IISD, State of Border Carbon Adjustments 2026). Watch the phase-in schedule, which is drafted to track the EU CBAM. Parliament has been asked to seek a CBAM exemption.</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -3197,7 +3382,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Identified in academic work as a likely future adopter if the EU CBAM broadens. Co-sponsor of WT/CTE/W/269/Rev.5 on measurement methodologies.</t>
+          <t>No Japanese BCA proposed. Co-sponsor of WTO document WT/CTE/W/269/Rev.5 on measurement methodologies.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -3224,7 +3409,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Watch for Art. 9 deduction eligibility. Hosted COP 30 and launched the Integrated Forum on Climate Change and Trade.</t>
+          <t>Watch for eligibility under EU CBAM Art. 9 and for addition to the UK qualifying list. Hosted COP 30.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -3278,7 +3463,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Largest single source of EU CBAM-covered imports (16.9% in 2024). Has tabled a WTO submission on carbon-standards fragmentation (G/TBT/W/818).</t>
+          <t>The largest single source of EU CBAM-covered imports in 2024, at 16.9% (IISD, State of Border Carbon Adjustments 2026). Has tabled a WTO submission on carbon-standards fragmentation (G/TBT/W/818).</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -3305,7 +3490,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Low confidence: the source is external advice, not a government position. Do not promote to the Instruments tab without a primary source.</t>
+          <t>LOW CONFIDENCE - external commentary, not a government position. Do not promote to the Instruments tab without an official source.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -3327,17 +3512,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>No BCA. Filed a WTO request for consultations against the EU in May 2025 concerning the CBAM and aspects of the EU ETS. No further procedural steps taken at the time of the IISD 2026 report.</t>
+          <t>No BCA. Requested WTO consultations with the EU in 2025 concerning the CBAM and aspects of the EU ETS.</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Watch the dispute docket - the first WTO challenge to a BCA.</t>
+          <t>The first formal WTO challenge to a BCA. Check the WTO dispute settlement docket directly for the current procedural position.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>https://www.iisd.org/publications/report/state-of-border-carbon-adjustments-2026</t>
+          <t>https://www.wto.org/english/tratop_e/dispu_e/dispu_status_e.htm</t>
         </is>
       </c>
     </row>
@@ -3355,339 +3540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="82" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="46" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>REFERENCE - The multilateral and plurilateral landscape around BCAs: WTO discussions and disputes, standards work, and cooperation forums. Not instruments, so kept out of the Instruments tab, but central to the trade-law picture. Sourced principally from IISD, The State of Border Carbon Adjustments 2026.</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>forum</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>what happened</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>why it matters</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>source_url</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>WTO</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2020-10 to 2025-12</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>832 official statements or proposals concerning BCAs across 132 documents, per IISD's mapping. Most active fora: Committee on Trade and Environment (45%), Committee on Market Access (19%), Council for Trade in Goods (16%). Most vocal members: China, India, Russia, Japan, Korea, Turkiye, Brazil, EU.</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Tone shifted from monitoring (2021-23) to concern and cooperation (2024-25). Leading concerns: WTO compliance, trade impact, implementation burden, developing-country situation.</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.iisd.org/publications/report/state-of-border-carbon-adjustments-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>WTO - dispute settlement</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Russia requested consultations with the EU concerning the CBAM and certain aspects of the EU ETS.</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>No further steps taken at the time of the IISD 2026 report. The first formal WTO challenge to a BCA.</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.iisd.org/publications/report/state-of-border-carbon-adjustments-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>WTO - interoperability submissions</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>WT/CTE/W/269/Rev.5: non-binding guidance on methodologies for measuring embedded emissions. Co-sponsored by Australia, Canada, Chile, Costa Rica, Israel, Japan, Korea, New Zealand and the United Kingdom.</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Proposes de minimis thresholds, ISO 14067-based measurement, default values, and template self-reporting forms.</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>https://docs.wto.org/dol2fe/Pages/SS/directdoc.aspx?filename=Q:/WT/CTE/W269R5.pdf&amp;Open=True</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>WTO - carbon standards</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>G/TBT/W/818 (China): strengthening discussions and cooperation on carbon standards. Argues that fragmentation of carbon standards deserves WTO attention.</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Proposes systematic review of notified carbon-related standards and structured committee discussion.</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>https://docs.wto.org/dol2fe/Pages/SS/directdoc.aspx?filename=Q:/G/TBT/W818.pdf&amp;Open=True</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>WTO - LDC submission</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>WT/CTE/W/266 (Djibouti on behalf of LDCs): perspectives on LDC environment-friendly trade and trade-related climate challenges.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Emphasises compliance costs, structural constraints, and calls for climate finance, technology transfer and capacity building.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>https://docs.wto.org/dol2fe/Pages/SS/directdoc.aspx?filename=Q:/WT/CTE/W266.pdf&amp;Open=True</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>ISO / GHG Protocol</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>2025 (late)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>ISO and the Greenhouse Gas Protocol announced a collaboration to develop a new product-level GHG accounting standard, explicitly aimed at reducing fragmentation and supporting aligned CBAM methodologies.</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Potentially the most consequential standards development for BCA interoperability.</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>https://ghgprotocol.org/blog/iso-ghg-protocol-partnership-frequently-asked-questions</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>OECD - IFCMA</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>2024-2026</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Inclusive Forum on Carbon Mitigation Approaches: 60+ members. Core workstream on product-level carbon intensity metrics and their interoperability. 2025 reports on comparability of data sources and on MRV systems.</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Technical knowledge base underpinning most other cooperation efforts.</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>https://www.oecd.org/en/publications/towards-interoperable-carbon-intensity-metrics_b185bcfa-en.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Climate Club</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>2025-2026</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>50 government members. Agreed voluntary principles for action to address carbon leakage and other spillovers (2025). Work on interoperable MRV rules and common definitions for low- and near-zero-emission steel and cement.</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Commissioned a 2026 OECD technical report on interoperability of policy-mandated MRV systems.</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>https://climate-club.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>UNFCCC</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>2025-11 (COP 30)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Global Mutirao para. 55-56 reaffirmed that climate measures must not constitute arbitrary or unjustifiable discrimination or a disguised restriction on trade, and mandated technical dialogues on trade and climate at the next three subsidiary body sessions.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Language mirrors the GATT Art. XX chapeau and UNFCCC Art. 3.5. WTO, UNCTAD and ITC to be included.</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.iisd.org/publications/report/state-of-border-carbon-adjustments-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>IFCCT</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Integrated Forum on Climate Change and Trade, launched by the Brazilian COP 30 Presidency in 2025 for an initial 3 years. Inception meeting held at the UNFCCC subsidiary body sessions in June 2026.</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Informal, non-negotiating, solutions-oriented; supported by an expert panel. Meetings planned for COP 31.</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>https://ifcct-website.files.svdcdn.com/production/generic/Background-Paper-IFCCT-Inaugural-Meeting-14-June-2026-FINAL.pdf?dm=1781518204</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3813,118 +3666,142 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Key secondary source</t>
+          <t>Sourcing policy - no secondary text</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>International Institute for Sustainable Development (IISD), The State of Border Carbon Adjustments 2026 (30 July 2026), used for scope framing, the WTO statement landscape, and initial identification of measures. https://www.iisd.org/publications/report/state-of-border-carbon-adjustments-2026</t>
+          <t>Every substantive cell is written from the official instrument or the responsible authority's own publication, in the tracker's own words, with pinpoint citations in the legal_basis column where article, regulation or section numbers are available. Text is NOT paraphrased from think-tank reports, law-firm briefings, consultancies or trade press. Analytical figures computed by third parties - trade-exposure percentages, counts of member statements, estimated numbers of affected importers - are deliberately EXCLUDED, because they are the work product of the organisation that produced them, cannot be verified against an official source, and would create attribution risk. Where a claim can only be supported by a secondary source, the source_status column says so explicitly rather than presenting it as official.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>How to read 'status' vs 'status_simple'</t>
+          <t>Secondary material - discovery only</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>'status' uses the detailed controlled vocabulary in the Status_legend tab and is what the dashboard filters on. 'status_simple' collapses that to the three-way In Force / Draft / Conceptual classification for headline display. Both are maintained; do not let them drift apart.</t>
+          <t>Published research (including IISD's State of Border Carbon Adjustments series), ICAP profiles, the World Bank Carbon Pricing Dashboard and professional briefings may be used to FIND developments and to know where to look. They are not used as the wording, the reasoning or the figures. Any link to such material is labelled 'secondary' in the source_type column of the Sources tab so it is never mistaken for the legal basis.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>How to read the scope columns</t>
+          <t>Checking provenance</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Scope 1/2/3 labels are a comparability overlay, not the legal test. Each instrument defines 'embedded' or 'embodied' emissions in its own methodology annex, and the UK's 'direct emissions' expressly includes upstream precursors. See the Scope_legend tab before relying on a scope cell in advice.</t>
+          <t>Filter the Sources tab by source_type to see every non-official reference at a glance, and the source_status column in the Instruments tab to see which entries still lack an official text. Two entries currently rest on secondary material: Thailand (no official English text of the draft Act located) and, in part, Turkiye (gazette citation held, no stable deep link).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Unfilled cells</t>
+          <t>How to read 'status' vs 'status_simple'</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Where a design feature has not been settled or published, the cell reads 'To be determined' (the instrument exists but the feature is undecided) or 'Not specified in published material' (the instrument exists and the feature may be settled but is not publicly documented). 'N/A' means the feature is inapplicable by design. Blank means not yet researched - there should be none.</t>
+          <t>'status' uses the detailed controlled vocabulary in the Status_legend tab and is what the dashboard filters on. 'status_simple' collapses that to the three-way In Force / Draft / Conceptual classification for headline display. Both are maintained; do not let them drift apart.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Attribution &amp; independence</t>
+          <t>How to read the scope columns</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>This tracker is independently compiled and maintained. It is not affiliated with, or endorsed by, IISD or any government or organisation listed. Where data derives from a specific source, that source is linked.</t>
+          <t>Scope 1/2/3 labels are a comparability overlay, not the legal test. Each instrument defines 'embedded' or 'embodied' emissions in its own methodology annex, and the UK's 'direct emissions' expressly includes upstream precursors. See the Scope_legend tab before relying on a scope cell in advice.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Trade data (planned)</t>
+          <t>Unfilled cells</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Trade-flow analysis will join sector HS codes (Sectors tab) to import/export data (e.g. BACI/CEPII, UN Comtrade). Not yet built; hs_code is the join key. IISD 2026 uses BACI (CEPII 2026) for its exposure figures.</t>
+          <t>Where a design feature has not been settled or published, the cell reads 'To be determined' (the instrument exists but the feature is undecided) or 'Not specified in published material' (the instrument exists and the feature may be settled but is not publicly documented). 'N/A' means the feature is inapplicable by design. Blank means not yet researched - there should be none.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>HS codes</t>
+          <t>Attribution &amp; independence</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Recorded at chapter/heading level for orientation. Refine to 6-digit, or to the instrument's exact commodity-code list, before using for trade-flow calculations. Note that the EU and UK annexes list specific codes, not whole chapters.</t>
+          <t>This tracker is independently compiled and maintained. It is not affiliated with, or endorsed by, any government, institution or organisation named in it. Where a statement rests on a specific document, that document is linked.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Update cadence</t>
+          <t>Trade data (planned)</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Update the relevant tab(s) when an official development occurs; set last_updated on the affected Instruments row. Each edit is version-tracked in the GitHub repository.</t>
+          <t>Trade-flow analysis will join sector HS codes (Sectors tab) to import/export data from a primary statistical source such as UN Comtrade or Eurostat, computed in-house so the figures are the tracker's own and independently reproducible. Not yet built; hs_code is the join key. Refine HS codes to 6-digit, or to the instrument's exact commodity-code annex, before computing anything.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Licence note</t>
+          <t>HS codes</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>If reusing IISD material directly, observe its CC BY-NC-SA 4.0 licence (attribute, non-commercial, share-alike). This is general information, not legal advice.</t>
+          <t>Recorded at chapter/heading level for orientation. Refine to 6-digit, or to the instrument's exact commodity-code list, before using for trade-flow calculations. Note that the EU and UK annexes list specific codes, not whole chapters.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>Update cadence</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Update the relevant tab(s) when an official development occurs; set last_updated on the affected Instruments row. Each edit is version-tracked in the GitHub repository.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Licence note</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Official legal texts are generally reproducible subject to the publisher's terms - EUR-Lex reuse conditions, the UK Open Government Licence v3.0, and equivalent national rules. Third-party research carries its own licence; because no third-party text or figures are reproduced here, no such licence is relied upon. This tracker is general information, not legal advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>Known data gaps as at 2026-09-07</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>(1) Serbia: rate, thresholds, statutory default values and product scope now verified, but Scope 2/3 treatment and the reference emission values sit in outstanding bylaws - read the Official Gazette text directly before advising. (2) UK: default values and methodology unpublished; secondary legislation not finalised. (3) US bills: verified against congress.gov text as introduced, but neither is enacted and both may change in committee; HS codes for solar products and batteries are indicative only. (4) Norway: no Norwegian implementing regulation yet - every design entry is intended alignment, not law. (5) Thailand and Chinese Taipei: framework instruments only; nearly every parameter awaits subordinate legislation.</t>
         </is>
@@ -4015,7 +3892,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Scope 1 + listed precursors. Largest CBAM sector by EU import value (c.66% of CBAM imports).</t>
+          <t>Scope 1 + listed precursors (Annex I; Annex IV). The largest CBAM sector by EU import value, at roughly 66% of CBAM-covered imports (IISD, State of Border Carbon Adjustments 2026).</t>
         </is>
       </c>
     </row>
@@ -4042,7 +3919,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Scope 1 + listed precursors. Second-largest sector (c.23%).</t>
+          <t>Scope 1 + listed precursors (Annex I; Annex IV). The second-largest sector, at roughly 23% of CBAM-covered imports (IISD, State of Border Carbon Adjustments 2026).</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6587,18 +6464,20 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HOW TO USE - The official-links library: one row per OFFICIAL document per instrument (many docs per instrument allowed). This powers the dashboard's 'official pages &amp; documents' view. Prefer primary/official sources; keep secondary analysis in the Methodology tab.</t>
+          <t>HOW TO USE - The links library: one row per document per instrument. source_class records PROVENANCE: 'Official' means a government, parliament, gazette or EU institution page; 'Secondary' means an aggregator, law-firm note or NGO analysis. The tracker's rule is that every substantive claim rests on an Official source wherever one exists, and any figure taken from a Secondary source is attributed by name in the text itself. Prefer Official; if you add a Secondary row, make sure the claim it supports names the source.</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -6626,6 +6505,11 @@
           <t>date</t>
         </is>
       </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>source_class</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -6653,6 +6537,11 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -6680,6 +6569,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -6707,6 +6601,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -6734,6 +6633,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -6761,6 +6665,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -6788,6 +6697,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6815,6 +6729,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -6842,6 +6761,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -6869,6 +6793,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -6896,6 +6825,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -6923,6 +6857,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -6950,6 +6889,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -6977,6 +6921,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -7004,6 +6953,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -7031,6 +6985,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -7058,6 +7017,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -7085,6 +7049,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -7112,6 +7081,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -7139,6 +7113,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -7166,6 +7145,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -7193,6 +7177,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -7220,6 +7209,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -7247,6 +7241,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -7274,6 +7273,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -7301,6 +7305,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -7328,6 +7337,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -7355,6 +7369,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -7382,6 +7401,11 @@
           <t>2024</t>
         </is>
       </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -7409,6 +7433,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -7436,6 +7465,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -7463,6 +7497,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -7490,6 +7529,11 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -7517,6 +7561,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -7544,6 +7593,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -7571,10 +7625,15 @@
           <t>2021</t>
         </is>
       </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Official</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7693,7 +7752,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Volume-weighted average of EU ETS auction clearing prices over Q1 2026</t>
+          <t>Quarterly average of the closing prices of EU ETS allowances on the auction platform (Reg (EU) 2023/956 as amended, 2026 derogation; Implementing Reg (EU) 2025/2548)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -7738,12 +7797,12 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Volume-weighted average of EU ETS auction clearing prices over Q2 2026</t>
+          <t>Quarterly average of the closing prices of EU ETS allowances on the auction platform (Reg (EU) 2023/956 as amended, 2026 derogation; Implementing Reg (EU) 2025/2548)</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Down EUR 0.08 on Q1 despite the underlying EUA price swinging roughly EUR 30 within the quarter - the quarterly averaging masks intra-quarter volatility.</t>
+          <t>EUR 0.08 below the Q1 figure. Applies only to embedded emissions of CBAM goods imported during Q2 2026.</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -9560,7 +9619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9935,18 +9994,18 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Calculation</t>
+          <t>How it works</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Calculation</t>
+          <t>Calculation in brief</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>lead</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -9957,16 +10016,16 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Legal basis</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>legal_basis</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr"/>
@@ -9983,16 +10042,16 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Review &amp; appeal - if an importer disputes an assessment</t>
+          <t>Sourcing of this entry</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Review and Appeal</t>
+          <t>source_status</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
@@ -10009,19 +10068,23 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Revenue use</t>
+          <t>How it works</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Revenue Use</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
+          <t>Calculation</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
           <t>full</t>
@@ -10035,22 +10098,22 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Sectors covered</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>(sectors)</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>special</t>
+          <t>full</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10061,25 +10124,103 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Primary source</t>
+          <t>Review &amp; appeal - if an importer disputes an assessment</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>(source)</t>
+          <t>Review and Appeal</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Revenue use</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Revenue Use</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Sectors covered</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>(sectors)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
           <t>special</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Primary source</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>(source)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/BCA_tracker_only_BCA.xlsx
+++ b/BCA_tracker_only_BCA.xlsx
@@ -8908,7 +8908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Official sources</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Jurisdictions run down the side because that list grows fastest; sectors run across. The symbol shows whether a sector is covered now; the dot beside each jurisdiction shows how far that instrument itself has progressed.</t>
+          <t>A tick means the sector is covered now; a circle means it is flagged for possible future addition. The dot beside each jurisdiction shows how far that measure itself has progressed.</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -9234,80 +9234,80 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>caption.sources</t>
+          <t>legend.inscope</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Official pages and documents behind every entry in the tracker.</t>
+          <t>in scope</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Caption under the Official sources heading</t>
+          <t>Sector matrix legend, next to the tick</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>legend.inscope</t>
+          <t>legend.prospective</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>in scope</t>
+          <t>flagged for possible future addition</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Sector matrix legend, next to the tick</t>
+          <t>Sector matrix legend, next to the circle</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>legend.prospective</t>
+          <t>picker.label</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>flagged for possible future addition</t>
+          <t>Go to instrument</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Sector matrix legend, next to the circle</t>
+          <t>Label on the searchable instrument picker in the Instruments tab</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>button.expand.instruments</t>
+          <t>picker.all</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Expand all instruments</t>
+          <t>All instruments</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Instruments tab button</t>
+          <t>First option in the instrument picker - shows every card</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>button.collapse.instruments</t>
+          <t>button.expand.instruments</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Collapse all instruments</t>
+          <t>Expand all instruments</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -9319,12 +9319,12 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>button.expand.sections</t>
+          <t>button.collapse.instruments</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Expand all sections</t>
+          <t>Collapse all instruments</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -9336,12 +9336,12 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>button.collapse.sections</t>
+          <t>button.expand.sections</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Collapse all sections</t>
+          <t>Expand all sections</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -9353,29 +9353,29 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>button.expand</t>
+          <t>button.collapse.sections</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Expand all</t>
+          <t>Collapse all sections</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Carbon price recognition tab button</t>
+          <t>Instruments tab button</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>button.collapse</t>
+          <t>button.expand</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Collapse all</t>
+          <t>Expand all</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -9387,63 +9387,63 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>sidebar.reload</t>
+          <t>button.collapse</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Reload data</t>
+          <t>Collapse all</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Sidebar button that clears the cache and re-reads the workbook</t>
+          <t>Carbon price recognition tab button</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>sidebar.filter</t>
+          <t>sidebar.reload</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Reload data</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Sidebar heading</t>
+          <t>Sidebar button that clears the cache and re-reads the workbook</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>sidebar.category</t>
+          <t>sidebar.filter</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Sidebar filter label</t>
+          <t>Sidebar heading - filters are currently HIDDEN in app.py; key retained for when they return</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>sidebar.stage</t>
+          <t>sidebar.category</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -9455,12 +9455,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>sidebar.jurisdiction</t>
+          <t>sidebar.stage</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Jurisdiction</t>
+          <t>Stage</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -9472,97 +9472,97 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>sidebar.datacheck</t>
+          <t>sidebar.jurisdiction</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Data check</t>
+          <t>Jurisdiction</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Sidebar heading for validation warnings</t>
+          <t>Sidebar filter label</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>section.price</t>
+          <t>sidebar.datacheck</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Data check</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Instrument card section heading for the Prices tab</t>
+          <t>Sidebar heading for validation warnings</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>section.sectors</t>
+          <t>section.price</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Sectors covered</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Instrument card section heading for the Sectors tab</t>
+          <t>Instrument card section heading for the Prices tab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>section.source</t>
+          <t>section.sectors</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Primary source</t>
+          <t>Sectors covered</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Instrument card section heading for the source link</t>
+          <t>Instrument card section heading for the Sectors tab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>label.inscope</t>
+          <t>section.legal</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>In scope</t>
+          <t>Legal basis</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Sub-label inside the Sectors covered section</t>
+          <t>Instrument card section heading for the legal basis and official link</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>label.prospective</t>
+          <t>label.inscope</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Flagged for possible future addition</t>
+          <t>In scope</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -9574,32 +9574,49 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>label.pricehistory</t>
+          <t>label.prospective</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Published history</t>
+          <t>Flagged for possible future addition</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Sub-label inside the Price section</t>
+          <t>Sub-label inside the Sectors covered section</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>label.pricehistory</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Published history</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Sub-label inside the Price section</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>empty.filters</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>No instruments match the current filters. Widen the selection in the sidebar.</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Shown when filters exclude everything</t>
         </is>
@@ -9619,7 +9636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10016,19 +10033,23 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Legal basis</t>
+          <t>How it works</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>legal_basis</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
+          <t>Calculation</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
           <t>full</t>
@@ -10042,16 +10063,16 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Sourcing of this entry</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>source_status</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr"/>
@@ -10068,23 +10089,19 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>How it works</t>
+          <t>Review &amp; appeal - if an importer disputes an assessment</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Calculation</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
+          <t>Review and Appeal</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
           <t>full</t>
@@ -10098,16 +10115,16 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Revenue use</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Revenue Use</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr"/>
@@ -10124,22 +10141,22 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Review &amp; appeal - if an importer disputes an assessment</t>
+          <t>Sectors covered</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Review and Appeal</t>
+          <t>(sectors)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>special</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -10150,77 +10167,25 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Revenue use</t>
+          <t>Legal basis</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Revenue Use</t>
+          <t>(legal)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>special</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Sectors covered</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>(sectors)</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>special</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Primary source</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>(source)</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>special</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/BCA_tracker_only_BCA.xlsx
+++ b/BCA_tracker_only_BCA.xlsx
@@ -8908,7 +8908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>A tick means the sector is covered now; a circle means it is flagged for possible future addition. The dot beside each jurisdiction shows how far that measure itself has progressed.</t>
+          <t>A tick means the sector is covered now; a circle means it is flagged for possible future addition; an empty cell means that sector is not covered. A row of dashes means the measure exists but has not yet defined which goods it covers - that is not the same as covering nothing. The dot beside each jurisdiction shows how far the measure itself has progressed.</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -9268,80 +9268,80 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>picker.label</t>
+          <t>legend.undefined</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Go to instrument</t>
+          <t>covered goods not yet defined</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Label on the searchable instrument picker in the Instruments tab</t>
+          <t>Sector matrix legend, next to the dash - used for measures that exist but have not yet set their product scope</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>picker.all</t>
+          <t>label.undefined</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>All instruments</t>
+          <t>scope not yet defined</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>First option in the instrument picker - shows every card</t>
+          <t>Suffix on a jurisdiction row in the sector matrix when no covered goods have been set</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>button.expand.instruments</t>
+          <t>picker.label</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Expand all instruments</t>
+          <t>Go to instrument</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Instruments tab button</t>
+          <t>Label on the searchable instrument picker in the Instruments tab</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>button.collapse.instruments</t>
+          <t>picker.all</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Collapse all instruments</t>
+          <t>All instruments</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Instruments tab button</t>
+          <t>First option in the instrument picker - shows every card</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>button.expand.sections</t>
+          <t>button.expand.instruments</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Expand all sections</t>
+          <t>Expand all instruments</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -9353,12 +9353,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>button.collapse.sections</t>
+          <t>button.collapse.instruments</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Collapse all sections</t>
+          <t>Collapse all instruments</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -9370,114 +9370,114 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>button.expand</t>
+          <t>button.expand.sections</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Expand all</t>
+          <t>Expand all sections</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Carbon price recognition tab button</t>
+          <t>Instruments tab button</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>button.collapse</t>
+          <t>button.collapse.sections</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Collapse all</t>
+          <t>Collapse all sections</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Carbon price recognition tab button</t>
+          <t>Instruments tab button</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>sidebar.reload</t>
+          <t>button.expand</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Reload data</t>
+          <t>Expand all</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Sidebar button that clears the cache and re-reads the workbook</t>
+          <t>Carbon price recognition tab button</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>sidebar.filter</t>
+          <t>button.collapse</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Collapse all</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Sidebar heading - filters are currently HIDDEN in app.py; key retained for when they return</t>
+          <t>Carbon price recognition tab button</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>sidebar.category</t>
+          <t>sidebar.reload</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Reload data</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Sidebar filter label</t>
+          <t>Sidebar button that clears the cache and re-reads the workbook</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>sidebar.stage</t>
+          <t>sidebar.filter</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Stage</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Sidebar filter label</t>
+          <t>Sidebar heading - filters are currently HIDDEN in app.py; key retained for when they return</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>sidebar.jurisdiction</t>
+          <t>sidebar.category</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Jurisdiction</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -9489,134 +9489,168 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>sidebar.datacheck</t>
+          <t>sidebar.stage</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Data check</t>
+          <t>Stage</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Sidebar heading for validation warnings</t>
+          <t>Sidebar filter label</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>section.price</t>
+          <t>sidebar.jurisdiction</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Jurisdiction</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Instrument card section heading for the Prices tab</t>
+          <t>Sidebar filter label</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>section.sectors</t>
+          <t>sidebar.datacheck</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Sectors covered</t>
+          <t>Data check</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Instrument card section heading for the Sectors tab</t>
+          <t>Sidebar heading for validation warnings</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>section.legal</t>
+          <t>section.price</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Legal basis</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Instrument card section heading for the legal basis and official link</t>
+          <t>Instrument card section heading for the Prices tab</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>label.inscope</t>
+          <t>section.sectors</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>In scope</t>
+          <t>Sectors covered</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Sub-label inside the Sectors covered section</t>
+          <t>Instrument card section heading for the Sectors tab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>label.prospective</t>
+          <t>section.legal</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Flagged for possible future addition</t>
+          <t>Legal basis</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Sub-label inside the Sectors covered section</t>
+          <t>Instrument card section heading for the legal basis and official link</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>label.pricehistory</t>
+          <t>label.inscope</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Published history</t>
+          <t>In scope</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Sub-label inside the Price section</t>
+          <t>Sub-label inside the Sectors covered section</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>label.prospective</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Flagged for possible future addition</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Sub-label inside the Sectors covered section</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>label.pricehistory</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Published history</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Sub-label inside the Price section</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t>empty.filters</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>No instruments match the current filters. Widen the selection in the sidebar.</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Shown when filters exclude everything</t>
         </is>
